--- a/public/Coffee Grounds Data - Alteryx Output.xlsx
+++ b/public/Coffee Grounds Data - Alteryx Output.xlsx
@@ -13029,7 +13029,7 @@
         <v>45.4857142857143</v>
       </c>
       <c r="J203" s="2">
-        <v>70597.2525</v>
+        <v>75514.9625</v>
       </c>
       <c r="K203" s="2">
         <v>0</v>
@@ -13063,14 +13063,14 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Greenville Blvd &amp; Red Banks Rd</t>
+          <t>100 East 10th Street</t>
         </is>
       </c>
       <c r="D204" s="2">
-        <v>131.54</v>
+        <v>345.44</v>
       </c>
       <c r="E204" s="2">
-        <v>123.54</v>
+        <v>337.44</v>
       </c>
       <c r="F204" s="2">
         <v>7</v>
@@ -13084,30 +13084,30 @@
         </is>
       </c>
       <c r="I204" s="2">
-        <v>17.6485714285714</v>
+        <v>48.2057142857143</v>
       </c>
       <c r="J204" s="2">
-        <v>42031.6525</v>
+        <v>42245.5525</v>
       </c>
       <c r="K204" s="2">
         <v>0</v>
       </c>
       <c r="M204" s="2">
-        <v>12.68</v>
+        <v>0</v>
       </c>
       <c r="N204" s="2">
         <v>0</v>
       </c>
       <c r="O204" t="inlineStr">
         <is>
-          <t>Home to Red Banks</t>
+          <t>Red Banks to 10th Street</t>
         </is>
       </c>
       <c r="P204" s="2">
-        <v>7.5</v>
+        <v>1.9</v>
       </c>
       <c r="S204" s="2">
-        <v>19.02516</v>
+        <v>51.96576</v>
       </c>
     </row>
     <row r="205">
@@ -13121,20 +13121,20 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>100 East 10th Street</t>
+          <t>Greenville Blvd &amp; Red Banks Rd</t>
         </is>
       </c>
       <c r="D205" s="2">
-        <v>345.44</v>
+        <v>131.54</v>
       </c>
       <c r="E205" s="2">
-        <v>337.44</v>
+        <v>123.54</v>
       </c>
       <c r="F205" s="2">
         <v>7</v>
       </c>
       <c r="G205" s="2">
-        <v>994</v>
+        <v>0</v>
       </c>
       <c r="H205" t="inlineStr">
         <is>
@@ -13142,7 +13142,7 @@
         </is>
       </c>
       <c r="I205" s="2">
-        <v>48.2057142857143</v>
+        <v>17.6485714285714</v>
       </c>
       <c r="J205" s="2">
         <v>42369.0925</v>
@@ -13151,21 +13151,21 @@
         <v>0</v>
       </c>
       <c r="M205" s="2">
-        <v>0</v>
+        <v>12.68</v>
       </c>
       <c r="N205" s="2">
         <v>0</v>
       </c>
       <c r="O205" t="inlineStr">
         <is>
-          <t>Red Banks to 10th Street</t>
+          <t>Home to Red Banks</t>
         </is>
       </c>
       <c r="P205" s="2">
-        <v>1.9</v>
+        <v>7.5</v>
       </c>
       <c r="S205" s="2">
-        <v>51.96576</v>
+        <v>19.02516</v>
       </c>
     </row>
     <row r="206">
@@ -13192,7 +13192,7 @@
         <v>7</v>
       </c>
       <c r="G206" s="2">
-        <v>994</v>
+        <v>0</v>
       </c>
       <c r="H206" t="inlineStr">
         <is>
@@ -13237,14 +13237,14 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Greenville Blvd &amp; Red Banks Rd</t>
+          <t>100 East 10th Street</t>
         </is>
       </c>
       <c r="D207" s="2">
-        <v>224.56</v>
+        <v>426.98</v>
       </c>
       <c r="E207" s="2">
-        <v>216.56</v>
+        <v>418.98</v>
       </c>
       <c r="F207" s="2">
         <v>7</v>
@@ -13258,30 +13258,30 @@
         </is>
       </c>
       <c r="I207" s="2">
-        <v>30.9371428571429</v>
+        <v>59.8542857142857</v>
       </c>
       <c r="J207" s="2">
-        <v>42637.4325</v>
+        <v>42839.8525</v>
       </c>
       <c r="K207" s="2">
         <v>0</v>
       </c>
       <c r="M207" s="2">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N207" s="2">
         <v>0</v>
       </c>
       <c r="O207" t="inlineStr">
         <is>
-          <t>Home to Red Banks</t>
+          <t>Red Banks to 10th Street</t>
         </is>
       </c>
       <c r="P207" s="2">
-        <v>7.5</v>
+        <v>1.9</v>
       </c>
       <c r="S207" s="2">
-        <v>33.35024</v>
+        <v>64.52292</v>
       </c>
     </row>
     <row r="208">
@@ -13295,20 +13295,20 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>100 East 10th Street</t>
+          <t>Greenville Blvd &amp; Red Banks Rd</t>
         </is>
       </c>
       <c r="D208" s="2">
-        <v>426.98</v>
+        <v>224.56</v>
       </c>
       <c r="E208" s="2">
-        <v>418.98</v>
+        <v>216.56</v>
       </c>
       <c r="F208" s="2">
         <v>7</v>
       </c>
       <c r="G208" s="2">
-        <v>1001</v>
+        <v>7</v>
       </c>
       <c r="H208" t="inlineStr">
         <is>
@@ -13316,7 +13316,7 @@
         </is>
       </c>
       <c r="I208" s="2">
-        <v>59.8542857142857</v>
+        <v>30.9371428571429</v>
       </c>
       <c r="J208" s="2">
         <v>43056.4125</v>
@@ -13325,21 +13325,21 @@
         <v>0</v>
       </c>
       <c r="M208" s="2">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N208" s="2">
         <v>0</v>
       </c>
       <c r="O208" t="inlineStr">
         <is>
-          <t>Red Banks to 10th Street</t>
+          <t>Home to Red Banks</t>
         </is>
       </c>
       <c r="P208" s="2">
-        <v>1.9</v>
+        <v>7.5</v>
       </c>
       <c r="S208" s="2">
-        <v>64.52292</v>
+        <v>33.35024</v>
       </c>
     </row>
     <row r="209">
@@ -13366,7 +13366,7 @@
         <v>7</v>
       </c>
       <c r="G209" s="2">
-        <v>1001</v>
+        <v>7</v>
       </c>
       <c r="H209" t="inlineStr">
         <is>
@@ -13424,7 +13424,7 @@
         <v>7</v>
       </c>
       <c r="G210" s="2">
-        <v>1008</v>
+        <v>14</v>
       </c>
       <c r="H210" t="inlineStr">
         <is>
@@ -13540,7 +13540,7 @@
         <v>7</v>
       </c>
       <c r="G212" s="2">
-        <v>1008</v>
+        <v>14</v>
       </c>
       <c r="H212" t="inlineStr">
         <is>
@@ -13551,7 +13551,7 @@
         <v>20.1257142857143</v>
       </c>
       <c r="J212" s="2">
-        <v>44189.7125</v>
+        <v>75514.9625</v>
       </c>
       <c r="K212" s="2">
         <v>0</v>
@@ -13585,14 +13585,14 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Greenville Blvd &amp; Red Banks Rd</t>
+          <t>100 East 10th Street</t>
         </is>
       </c>
       <c r="D213" s="2">
-        <v>248.48</v>
+        <v>204.88</v>
       </c>
       <c r="E213" s="2">
-        <v>240.48</v>
+        <v>196.88</v>
       </c>
       <c r="F213" s="2">
         <v>7</v>
@@ -13606,10 +13606,10 @@
         </is>
       </c>
       <c r="I213" s="2">
-        <v>34.3542857142857</v>
+        <v>28.1257142857143</v>
       </c>
       <c r="J213" s="2">
-        <v>44430.1925</v>
+        <v>44386.5925</v>
       </c>
       <c r="K213" s="2">
         <v>0</v>
@@ -13622,19 +13622,19 @@
       </c>
       <c r="O213" t="inlineStr">
         <is>
-          <t>Home to Red Banks</t>
+          <t>Red Banks to 10th Street</t>
         </is>
       </c>
       <c r="P213" s="2">
-        <v>7.5</v>
+        <v>1.9</v>
       </c>
       <c r="R213" t="inlineStr">
         <is>
-          <t>Store closed early at 4pm due to the 10in of snow</t>
+          <t>Store was closed for the day due to snow storm. Wasn't able to haul one bin because it was inside of the store. Dropped off 2 fresh bins, will pick up the 3rd bin next Mon.</t>
         </is>
       </c>
       <c r="S213" s="2">
-        <v>37.03392</v>
+        <v>30.31952</v>
       </c>
     </row>
     <row r="214">
@@ -13648,20 +13648,20 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>100 East 10th Street</t>
+          <t>Greenville Blvd &amp; Red Banks Rd</t>
         </is>
       </c>
       <c r="D214" s="2">
-        <v>204.88</v>
+        <v>248.48</v>
       </c>
       <c r="E214" s="2">
-        <v>196.88</v>
+        <v>240.48</v>
       </c>
       <c r="F214" s="2">
         <v>7</v>
       </c>
       <c r="G214" s="2">
-        <v>1015</v>
+        <v>21</v>
       </c>
       <c r="H214" t="inlineStr">
         <is>
@@ -13669,7 +13669,7 @@
         </is>
       </c>
       <c r="I214" s="2">
-        <v>28.1257142857143</v>
+        <v>34.3542857142857</v>
       </c>
       <c r="J214" s="2">
         <v>44627.0725</v>
@@ -13685,19 +13685,19 @@
       </c>
       <c r="O214" t="inlineStr">
         <is>
-          <t>Red Banks to 10th Street</t>
+          <t>Home to Red Banks</t>
         </is>
       </c>
       <c r="P214" s="2">
-        <v>1.9</v>
+        <v>7.5</v>
       </c>
       <c r="R214" t="inlineStr">
         <is>
-          <t>Store was closed for the day due to snow storm. Wasn't able to haul one bin because it was inside of the store. Dropped off 2 fresh bins, will pick up the 3rd bin next Mon.</t>
+          <t>Store closed early at 4pm due to the 10in of snow</t>
         </is>
       </c>
       <c r="S214" s="2">
-        <v>30.31952</v>
+        <v>37.03392</v>
       </c>
     </row>
     <row r="215">
@@ -13724,7 +13724,7 @@
         <v>7</v>
       </c>
       <c r="G215" s="2">
-        <v>1015</v>
+        <v>21</v>
       </c>
       <c r="H215" t="inlineStr">
         <is>
@@ -13787,7 +13787,7 @@
         <v>2</v>
       </c>
       <c r="G216" s="2">
-        <v>1017</v>
+        <v>23</v>
       </c>
       <c r="H216" t="inlineStr">
         <is>
@@ -13832,14 +13832,14 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Greenville Blvd &amp; Red Banks Rd</t>
+          <t>100 East 10th Street</t>
         </is>
       </c>
       <c r="D217" s="2">
-        <v>248.16</v>
+        <v>508.86</v>
       </c>
       <c r="E217" s="2">
-        <v>240.16</v>
+        <v>500.86</v>
       </c>
       <c r="F217" s="2">
         <v>7</v>
@@ -13853,30 +13853,35 @@
         </is>
       </c>
       <c r="I217" s="2">
-        <v>34.3085714285714</v>
+        <v>71.5514285714286</v>
       </c>
       <c r="J217" s="2">
-        <v>45343.4525</v>
+        <v>45604.1525</v>
       </c>
       <c r="K217" s="2">
         <v>0</v>
       </c>
       <c r="M217" s="2">
-        <v>8.32</v>
+        <v>21.18</v>
       </c>
       <c r="N217" s="2">
         <v>0</v>
       </c>
       <c r="O217" t="inlineStr">
         <is>
-          <t>Home to Red Banks</t>
+          <t>Home to 100 East 10th Street</t>
         </is>
       </c>
       <c r="P217" s="2">
-        <v>7.5</v>
+        <v>7.7</v>
+      </c>
+      <c r="R217" t="inlineStr">
+        <is>
+          <t>3 bins; 3rd bin leftover from the snowstorm last week</t>
+        </is>
       </c>
       <c r="S217" s="2">
-        <v>36.98464</v>
+        <v>77.13244</v>
       </c>
     </row>
     <row r="218">
@@ -13890,20 +13895,20 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>100 East 10th Street</t>
+          <t>Greenville Blvd &amp; Red Banks Rd</t>
         </is>
       </c>
       <c r="D218" s="2">
-        <v>508.86</v>
+        <v>248.16</v>
       </c>
       <c r="E218" s="2">
-        <v>500.86</v>
+        <v>240.16</v>
       </c>
       <c r="F218" s="2">
         <v>7</v>
       </c>
       <c r="G218" s="2">
-        <v>1022</v>
+        <v>28</v>
       </c>
       <c r="H218" t="inlineStr">
         <is>
@@ -13911,7 +13916,7 @@
         </is>
       </c>
       <c r="I218" s="2">
-        <v>71.5514285714286</v>
+        <v>34.3085714285714</v>
       </c>
       <c r="J218" s="2">
         <v>45844.3125</v>
@@ -13920,26 +13925,21 @@
         <v>0</v>
       </c>
       <c r="M218" s="2">
-        <v>21.18</v>
+        <v>8.32</v>
       </c>
       <c r="N218" s="2">
         <v>0</v>
       </c>
       <c r="O218" t="inlineStr">
         <is>
-          <t>Home to 100 East 10th Street</t>
+          <t>Home to Red Banks</t>
         </is>
       </c>
       <c r="P218" s="2">
-        <v>7.7</v>
-      </c>
-      <c r="R218" t="inlineStr">
-        <is>
-          <t>3 bins; 3rd bin leftover from the snowstorm last week</t>
-        </is>
+        <v>7.5</v>
       </c>
       <c r="S218" s="2">
-        <v>77.13244</v>
+        <v>36.98464</v>
       </c>
     </row>
     <row r="219">
@@ -13966,7 +13966,7 @@
         <v>5</v>
       </c>
       <c r="G219" s="2">
-        <v>1022</v>
+        <v>28</v>
       </c>
       <c r="H219" t="inlineStr">
         <is>
@@ -14006,14 +14006,14 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Greenville Blvd &amp; Red Banks Rd</t>
+          <t>100 East 10th Street</t>
         </is>
       </c>
       <c r="D220" s="2">
-        <v>186.6</v>
+        <v>373.56</v>
       </c>
       <c r="E220" s="2">
-        <v>178.6</v>
+        <v>365.56</v>
       </c>
       <c r="F220" s="2">
         <v>7</v>
@@ -14027,30 +14027,30 @@
         </is>
       </c>
       <c r="I220" s="2">
-        <v>25.5142857142857</v>
+        <v>52.2228571428571</v>
       </c>
       <c r="J220" s="2">
-        <v>46328.0325</v>
+        <v>46514.9925</v>
       </c>
       <c r="K220" s="2">
         <v>0</v>
       </c>
       <c r="M220" s="2">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="N220" s="2">
         <v>0</v>
       </c>
       <c r="O220" t="inlineStr">
         <is>
-          <t>Home to Red Banks</t>
+          <t>Red Banks to 10th Street</t>
         </is>
       </c>
       <c r="P220" s="2">
-        <v>7.5</v>
+        <v>1.9</v>
       </c>
       <c r="S220" s="2">
-        <v>27.5044</v>
+        <v>56.29624</v>
       </c>
     </row>
     <row r="221">
@@ -14064,20 +14064,20 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>100 East 10th Street</t>
+          <t>Greenville Blvd &amp; Red Banks Rd</t>
         </is>
       </c>
       <c r="D221" s="2">
-        <v>373.56</v>
+        <v>186.6</v>
       </c>
       <c r="E221" s="2">
-        <v>365.56</v>
+        <v>178.6</v>
       </c>
       <c r="F221" s="2">
         <v>7</v>
       </c>
       <c r="G221" s="2">
-        <v>1029</v>
+        <v>35</v>
       </c>
       <c r="H221" t="inlineStr">
         <is>
@@ -14085,7 +14085,7 @@
         </is>
       </c>
       <c r="I221" s="2">
-        <v>52.2228571428571</v>
+        <v>25.5142857142857</v>
       </c>
       <c r="J221" s="2">
         <v>46693.5925</v>
@@ -14094,21 +14094,21 @@
         <v>0</v>
       </c>
       <c r="M221" s="2">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="N221" s="2">
         <v>0</v>
       </c>
       <c r="O221" t="inlineStr">
         <is>
-          <t>Red Banks to 10th Street</t>
+          <t>Home to Red Banks</t>
         </is>
       </c>
       <c r="P221" s="2">
-        <v>1.9</v>
+        <v>7.5</v>
       </c>
       <c r="S221" s="2">
-        <v>56.29624</v>
+        <v>27.5044</v>
       </c>
     </row>
     <row r="222">
@@ -14135,7 +14135,7 @@
         <v>7</v>
       </c>
       <c r="G222" s="2">
-        <v>1029</v>
+        <v>35</v>
       </c>
       <c r="H222" t="inlineStr">
         <is>
@@ -14180,14 +14180,14 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Greenville Blvd &amp; Red Banks Rd</t>
+          <t>100 East 10th Street</t>
         </is>
       </c>
       <c r="D223" s="2">
-        <v>294.18</v>
+        <v>422.36</v>
       </c>
       <c r="E223" s="2">
-        <v>286.18</v>
+        <v>414.36</v>
       </c>
       <c r="F223" s="2">
         <v>7</v>
@@ -14201,30 +14201,35 @@
         </is>
       </c>
       <c r="I223" s="2">
-        <v>40.8828571428571</v>
+        <v>59.1942857142857</v>
       </c>
       <c r="J223" s="2">
-        <v>47469.0325</v>
+        <v>47597.2125</v>
       </c>
       <c r="K223" s="2">
         <v>0</v>
       </c>
       <c r="M223" s="2">
-        <v>0</v>
+        <v>17.8</v>
       </c>
       <c r="N223" s="2">
         <v>0</v>
       </c>
       <c r="O223" t="inlineStr">
         <is>
-          <t>Home to Red Banks</t>
+          <t>Red Banks to 10th Street</t>
         </is>
       </c>
       <c r="P223" s="2">
-        <v>7.5</v>
+        <v>1.9</v>
+      </c>
+      <c r="R223" t="inlineStr">
+        <is>
+          <t>Over bin capacity, some grounds had to be thrown away. Will add 3rd bin.</t>
+        </is>
       </c>
       <c r="S223" s="2">
-        <v>44.07172</v>
+        <v>63.81144</v>
       </c>
     </row>
     <row r="224">
@@ -14238,20 +14243,20 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>100 East 10th Street</t>
+          <t>Greenville Blvd &amp; Red Banks Rd</t>
         </is>
       </c>
       <c r="D224" s="2">
-        <v>422.36</v>
+        <v>294.18</v>
       </c>
       <c r="E224" s="2">
-        <v>414.36</v>
+        <v>286.18</v>
       </c>
       <c r="F224" s="2">
         <v>7</v>
       </c>
       <c r="G224" s="2">
-        <v>1036</v>
+        <v>42</v>
       </c>
       <c r="H224" t="inlineStr">
         <is>
@@ -14259,7 +14264,7 @@
         </is>
       </c>
       <c r="I224" s="2">
-        <v>59.1942857142857</v>
+        <v>40.8828571428571</v>
       </c>
       <c r="J224" s="2">
         <v>47883.3925</v>
@@ -14268,26 +14273,21 @@
         <v>0</v>
       </c>
       <c r="M224" s="2">
-        <v>17.8</v>
+        <v>0</v>
       </c>
       <c r="N224" s="2">
         <v>0</v>
       </c>
       <c r="O224" t="inlineStr">
         <is>
-          <t>Red Banks to 10th Street</t>
+          <t>Home to Red Banks</t>
         </is>
       </c>
       <c r="P224" s="2">
-        <v>1.9</v>
-      </c>
-      <c r="R224" t="inlineStr">
-        <is>
-          <t>Over bin capacity, some grounds had to be thrown away. Will add 3rd bin.</t>
-        </is>
+        <v>7.5</v>
       </c>
       <c r="S224" s="2">
-        <v>63.81144</v>
+        <v>44.07172</v>
       </c>
     </row>
     <row r="225">
@@ -14314,7 +14314,7 @@
         <v>7</v>
       </c>
       <c r="G225" s="2">
-        <v>1036</v>
+        <v>42</v>
       </c>
       <c r="H225" t="inlineStr">
         <is>
@@ -14440,7 +14440,7 @@
         <v>5</v>
       </c>
       <c r="G227" s="2">
-        <v>1041</v>
+        <v>47</v>
       </c>
       <c r="H227" t="inlineStr">
         <is>
@@ -14498,7 +14498,7 @@
         <v>7</v>
       </c>
       <c r="G228" s="2">
-        <v>1043</v>
+        <v>49</v>
       </c>
       <c r="H228" t="inlineStr">
         <is>
@@ -14509,7 +14509,7 @@
         <v>37.24</v>
       </c>
       <c r="J228" s="2">
-        <v>70597.2525</v>
+        <v>75514.9625</v>
       </c>
       <c r="K228" s="2">
         <v>0</v>
@@ -14543,14 +14543,14 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Greenville Blvd &amp; Red Banks Rd</t>
+          <t>100 East 10th Street</t>
         </is>
       </c>
       <c r="D229" s="2">
-        <v>211.49</v>
+        <v>457.5</v>
       </c>
       <c r="E229" s="2">
-        <v>203.49</v>
+        <v>449.5</v>
       </c>
       <c r="F229" s="2">
         <v>7</v>
@@ -14564,10 +14564,10 @@
         </is>
       </c>
       <c r="I229" s="2">
-        <v>29.07</v>
+        <v>64.2142857142857</v>
       </c>
       <c r="J229" s="2">
-        <v>49514.8825</v>
+        <v>49760.8925</v>
       </c>
       <c r="K229" s="2">
         <v>0</v>
@@ -14580,14 +14580,14 @@
       </c>
       <c r="O229" t="inlineStr">
         <is>
-          <t>Home to Red Banks</t>
+          <t>Home to 100 East 10th Street</t>
         </is>
       </c>
       <c r="P229" s="2">
-        <v>7.5</v>
+        <v>11.4</v>
       </c>
       <c r="S229" s="2">
-        <v>31.33746</v>
+        <v>69.223</v>
       </c>
     </row>
     <row r="230">
@@ -14601,20 +14601,20 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Stanton Sq &amp; Arlington Dr</t>
+          <t>Greenville Blvd &amp; Red Banks Rd</t>
         </is>
       </c>
       <c r="D230" s="2">
-        <v>527.48</v>
+        <v>211.49</v>
       </c>
       <c r="E230" s="2">
-        <v>519.48</v>
+        <v>203.49</v>
       </c>
       <c r="F230" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G230" s="2">
-        <v>1050</v>
+        <v>56</v>
       </c>
       <c r="H230" t="inlineStr">
         <is>
@@ -14622,10 +14622,10 @@
         </is>
       </c>
       <c r="I230" s="2">
-        <v>57.72</v>
+        <v>29.07</v>
       </c>
       <c r="J230" s="2">
-        <v>50034.3625</v>
+        <v>49964.3825</v>
       </c>
       <c r="K230" s="2">
         <v>0</v>
@@ -14638,14 +14638,14 @@
       </c>
       <c r="O230" t="inlineStr">
         <is>
-          <t>10th St to Stanton to Home</t>
+          <t>Home to Red Banks</t>
         </is>
       </c>
       <c r="P230" s="2">
-        <v>13.7</v>
+        <v>7.5</v>
       </c>
       <c r="S230" s="2">
-        <v>79.99992</v>
+        <v>31.33746</v>
       </c>
     </row>
     <row r="231">
@@ -14659,20 +14659,20 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>100 East 10th Street</t>
+          <t>Stanton Sq &amp; Arlington Dr</t>
         </is>
       </c>
       <c r="D231" s="2">
-        <v>457.5</v>
+        <v>527.48</v>
       </c>
       <c r="E231" s="2">
-        <v>449.5</v>
+        <v>519.48</v>
       </c>
       <c r="F231" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G231" s="2">
-        <v>1050</v>
+        <v>56</v>
       </c>
       <c r="H231" t="inlineStr">
         <is>
@@ -14680,7 +14680,7 @@
         </is>
       </c>
       <c r="I231" s="2">
-        <v>49.9444444444444</v>
+        <v>74.2114285714286</v>
       </c>
       <c r="J231" s="2">
         <v>50483.8625</v>
@@ -14696,14 +14696,14 @@
       </c>
       <c r="O231" t="inlineStr">
         <is>
-          <t>Home to 100 East 10th Street</t>
+          <t>10th St to Stanton to Home</t>
         </is>
       </c>
       <c r="P231" s="2">
-        <v>11.4</v>
+        <v>13.7</v>
       </c>
       <c r="S231" s="2">
-        <v>69.223</v>
+        <v>79.99992</v>
       </c>
     </row>
     <row r="232">
@@ -14778,20 +14778,20 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Stanton Sq &amp; Arlington Dr</t>
+          <t>Greenville Blvd &amp; Red Banks Rd</t>
         </is>
       </c>
       <c r="D233" s="2">
-        <v>313.06</v>
+        <v>254.82</v>
       </c>
       <c r="E233" s="2">
-        <v>305.06</v>
+        <v>246.82</v>
       </c>
       <c r="F233" s="2">
         <v>7</v>
       </c>
       <c r="G233" s="2">
-        <v>1057</v>
+        <v>63</v>
       </c>
       <c r="H233" t="inlineStr">
         <is>
@@ -14799,13 +14799,16 @@
         </is>
       </c>
       <c r="I233" s="2">
-        <v>43.58</v>
+        <v>35.26</v>
       </c>
       <c r="J233" s="2">
-        <v>51076.3025</v>
+        <v>51018.0625</v>
       </c>
       <c r="K233" s="2">
-        <v>0</v>
+        <v>102</v>
+      </c>
+      <c r="L233" s="1">
+        <v>46099.000000</v>
       </c>
       <c r="M233" s="2">
         <v>0</v>
@@ -14815,14 +14818,14 @@
       </c>
       <c r="O233" t="inlineStr">
         <is>
-          <t>10th Street to Stanton Sq</t>
+          <t>Stanton to Red Banks to home</t>
         </is>
       </c>
       <c r="P233" s="2">
-        <v>2.4</v>
+        <v>10.8</v>
       </c>
       <c r="S233" s="2">
-        <v>46.97924</v>
+        <v>38.01028</v>
       </c>
     </row>
     <row r="234">
@@ -14836,20 +14839,20 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Greenville Blvd &amp; Red Banks Rd</t>
+          <t>Stanton Sq &amp; Arlington Dr</t>
         </is>
       </c>
       <c r="D234" s="2">
-        <v>254.82</v>
+        <v>313.06</v>
       </c>
       <c r="E234" s="2">
-        <v>246.82</v>
+        <v>305.06</v>
       </c>
       <c r="F234" s="2">
         <v>7</v>
       </c>
       <c r="G234" s="2">
-        <v>1057</v>
+        <v>63</v>
       </c>
       <c r="H234" t="inlineStr">
         <is>
@@ -14857,16 +14860,13 @@
         </is>
       </c>
       <c r="I234" s="2">
-        <v>35.26</v>
+        <v>43.58</v>
       </c>
       <c r="J234" s="2">
         <v>51323.1225</v>
       </c>
       <c r="K234" s="2">
-        <v>102</v>
-      </c>
-      <c r="L234" s="1">
-        <v>46099.000000</v>
+        <v>0</v>
       </c>
       <c r="M234" s="2">
         <v>0</v>
@@ -14876,14 +14876,14 @@
       </c>
       <c r="O234" t="inlineStr">
         <is>
-          <t>Stanton to Red Banks to home</t>
+          <t>10th Street to Stanton Sq</t>
         </is>
       </c>
       <c r="P234" s="2">
-        <v>10.8</v>
+        <v>2.4</v>
       </c>
       <c r="S234" s="2">
-        <v>38.01028</v>
+        <v>46.97924</v>
       </c>
     </row>
     <row r="235">
@@ -14921,7 +14921,7 @@
         <v>61.57</v>
       </c>
       <c r="J235" s="2">
-        <v>70597.2525</v>
+        <v>75514.9625</v>
       </c>
       <c r="K235" s="2">
         <v>0</v>
@@ -14968,7 +14968,7 @@
         <v>7</v>
       </c>
       <c r="G236" s="2">
-        <v>1064</v>
+        <v>70</v>
       </c>
       <c r="H236" t="inlineStr">
         <is>
@@ -15026,7 +15026,7 @@
         <v>7</v>
       </c>
       <c r="G237" s="2">
-        <v>1064</v>
+        <v>70</v>
       </c>
       <c r="H237" t="inlineStr">
         <is>
@@ -15071,14 +15071,14 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Greenville Blvd &amp; Red Banks Rd</t>
+          <t>100 East 10th Street</t>
         </is>
       </c>
       <c r="D238" s="2">
-        <v>247.4</v>
+        <v>595.08</v>
       </c>
       <c r="E238" s="2">
-        <v>239.4</v>
+        <v>587.08</v>
       </c>
       <c r="F238" s="2">
         <v>7</v>
@@ -15092,10 +15092,10 @@
         </is>
       </c>
       <c r="I238" s="2">
-        <v>34.2</v>
+        <v>83.8685714285714</v>
       </c>
       <c r="J238" s="2">
-        <v>52549.8625</v>
+        <v>52897.5425</v>
       </c>
       <c r="K238" s="2">
         <v>0</v>
@@ -15108,14 +15108,14 @@
       </c>
       <c r="O238" t="inlineStr">
         <is>
-          <t>Home to Red Banks</t>
+          <t>Red Banks to 10th to Home</t>
         </is>
       </c>
       <c r="P238" s="2">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
       <c r="S238" s="2">
-        <v>36.8676</v>
+        <v>90.41032</v>
       </c>
     </row>
     <row r="239">
@@ -15129,20 +15129,20 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>100 East 10th Street</t>
+          <t>Greenville Blvd &amp; Red Banks Rd</t>
         </is>
       </c>
       <c r="D239" s="2">
-        <v>595.08</v>
+        <v>247.4</v>
       </c>
       <c r="E239" s="2">
-        <v>587.08</v>
+        <v>239.4</v>
       </c>
       <c r="F239" s="2">
         <v>7</v>
       </c>
       <c r="G239" s="2">
-        <v>1071</v>
+        <v>77</v>
       </c>
       <c r="H239" t="inlineStr">
         <is>
@@ -15150,7 +15150,7 @@
         </is>
       </c>
       <c r="I239" s="2">
-        <v>83.8685714285714</v>
+        <v>34.2</v>
       </c>
       <c r="J239" s="2">
         <v>53136.9425</v>
@@ -15166,14 +15166,14 @@
       </c>
       <c r="O239" t="inlineStr">
         <is>
-          <t>Red Banks to 10th to Home</t>
+          <t>Home to Red Banks</t>
         </is>
       </c>
       <c r="P239" s="2">
-        <v>7.7</v>
+        <v>7.5</v>
       </c>
       <c r="S239" s="2">
-        <v>90.41032</v>
+        <v>36.8676</v>
       </c>
     </row>
     <row r="240">
@@ -15200,7 +15200,7 @@
         <v>7</v>
       </c>
       <c r="G240" s="2">
-        <v>1071</v>
+        <v>77</v>
       </c>
       <c r="H240" t="inlineStr">
         <is>
@@ -15245,14 +15245,14 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Greenville Blvd &amp; Red Banks Rd</t>
+          <t>100 East 10th Street</t>
         </is>
       </c>
       <c r="D241" s="2">
-        <v>244.56</v>
+        <v>405.96</v>
       </c>
       <c r="E241" s="2">
-        <v>236.56</v>
+        <v>397.96</v>
       </c>
       <c r="F241" s="2">
         <v>7</v>
@@ -15266,10 +15266,10 @@
         </is>
       </c>
       <c r="I241" s="2">
-        <v>33.7942857142857</v>
+        <v>56.8514285714286</v>
       </c>
       <c r="J241" s="2">
-        <v>53746.1625</v>
+        <v>53907.5625</v>
       </c>
       <c r="K241" s="2">
         <v>0</v>
@@ -15282,14 +15282,14 @@
       </c>
       <c r="O241" t="inlineStr">
         <is>
-          <t>Home to Red Banks</t>
+          <t>Red Banks to 10th to Home</t>
         </is>
       </c>
       <c r="P241" s="2">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
       <c r="S241" s="2">
-        <v>36.43024</v>
+        <v>61.28584</v>
       </c>
     </row>
     <row r="242">
@@ -15303,20 +15303,20 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>100 East 10th Street</t>
+          <t>Greenville Blvd &amp; Red Banks Rd</t>
         </is>
       </c>
       <c r="D242" s="2">
-        <v>405.96</v>
+        <v>244.56</v>
       </c>
       <c r="E242" s="2">
-        <v>397.96</v>
+        <v>236.56</v>
       </c>
       <c r="F242" s="2">
         <v>7</v>
       </c>
       <c r="G242" s="2">
-        <v>1078</v>
+        <v>84</v>
       </c>
       <c r="H242" t="inlineStr">
         <is>
@@ -15324,7 +15324,7 @@
         </is>
       </c>
       <c r="I242" s="2">
-        <v>56.8514285714286</v>
+        <v>33.7942857142857</v>
       </c>
       <c r="J242" s="2">
         <v>54144.1225</v>
@@ -15340,14 +15340,14 @@
       </c>
       <c r="O242" t="inlineStr">
         <is>
-          <t>Red Banks to 10th to Home</t>
+          <t>Home to Red Banks</t>
         </is>
       </c>
       <c r="P242" s="2">
-        <v>7.7</v>
+        <v>7.5</v>
       </c>
       <c r="S242" s="2">
-        <v>61.28584</v>
+        <v>36.43024</v>
       </c>
     </row>
     <row r="243">
@@ -15374,7 +15374,7 @@
         <v>7</v>
       </c>
       <c r="G243" s="2">
-        <v>1078</v>
+        <v>84</v>
       </c>
       <c r="H243" t="inlineStr">
         <is>
@@ -15419,14 +15419,14 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Greenville Blvd &amp; Red Banks Rd</t>
+          <t>100 East 10th Street</t>
         </is>
       </c>
       <c r="D244" s="2">
-        <v>201.5</v>
+        <v>414.9</v>
       </c>
       <c r="E244" s="2">
-        <v>193.5</v>
+        <v>406.9</v>
       </c>
       <c r="F244" s="2">
         <v>7</v>
@@ -15440,30 +15440,30 @@
         </is>
       </c>
       <c r="I244" s="2">
-        <v>27.6428571428571</v>
+        <v>58.1285714285714</v>
       </c>
       <c r="J244" s="2">
-        <v>54671.2425</v>
+        <v>54884.6425</v>
       </c>
       <c r="K244" s="2">
         <v>0</v>
       </c>
       <c r="M244" s="2">
-        <v>0</v>
+        <v>15.54</v>
       </c>
       <c r="N244" s="2">
         <v>0</v>
       </c>
       <c r="O244" t="inlineStr">
         <is>
-          <t>Home to Red Banks</t>
+          <t>Red Banks to 10th to Home</t>
         </is>
       </c>
       <c r="P244" s="2">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
       <c r="S244" s="2">
-        <v>29.799</v>
+        <v>62.6626</v>
       </c>
     </row>
     <row r="245">
@@ -15477,20 +15477,20 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>100 East 10th Street</t>
+          <t>Greenville Blvd &amp; Red Banks Rd</t>
         </is>
       </c>
       <c r="D245" s="2">
-        <v>414.9</v>
+        <v>201.5</v>
       </c>
       <c r="E245" s="2">
-        <v>406.9</v>
+        <v>193.5</v>
       </c>
       <c r="F245" s="2">
         <v>7</v>
       </c>
       <c r="G245" s="2">
-        <v>1085</v>
+        <v>91</v>
       </c>
       <c r="H245" t="inlineStr">
         <is>
@@ -15498,7 +15498,7 @@
         </is>
       </c>
       <c r="I245" s="2">
-        <v>58.1285714285714</v>
+        <v>27.6428571428571</v>
       </c>
       <c r="J245" s="2">
         <v>55078.1425</v>
@@ -15507,21 +15507,21 @@
         <v>0</v>
       </c>
       <c r="M245" s="2">
-        <v>15.54</v>
+        <v>0</v>
       </c>
       <c r="N245" s="2">
         <v>0</v>
       </c>
       <c r="O245" t="inlineStr">
         <is>
-          <t>Red Banks to 10th to Home</t>
+          <t>Home to Red Banks</t>
         </is>
       </c>
       <c r="P245" s="2">
-        <v>7.7</v>
+        <v>7.5</v>
       </c>
       <c r="S245" s="2">
-        <v>62.6626</v>
+        <v>29.799</v>
       </c>
     </row>
     <row r="246">
@@ -15548,7 +15548,7 @@
         <v>7</v>
       </c>
       <c r="G246" s="2">
-        <v>1085</v>
+        <v>91</v>
       </c>
       <c r="H246" t="inlineStr">
         <is>
@@ -15667,7 +15667,7 @@
         <v>7</v>
       </c>
       <c r="G248" s="2">
-        <v>1092</v>
+        <v>98</v>
       </c>
       <c r="H248" t="inlineStr">
         <is>
@@ -15725,7 +15725,7 @@
         <v>7</v>
       </c>
       <c r="G249" s="2">
-        <v>1092</v>
+        <v>98</v>
       </c>
       <c r="H249" t="inlineStr">
         <is>
@@ -15773,14 +15773,14 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Greenville Blvd &amp; Red Banks Rd</t>
+          <t>100 East 10th Street</t>
         </is>
       </c>
       <c r="D250" s="2">
-        <v>224.86</v>
+        <v>377.84</v>
       </c>
       <c r="E250" s="2">
-        <v>216.86</v>
+        <v>369.84</v>
       </c>
       <c r="F250" s="2">
         <v>7</v>
@@ -15794,30 +15794,30 @@
         </is>
       </c>
       <c r="I250" s="2">
-        <v>30.98</v>
+        <v>52.8342857142857</v>
       </c>
       <c r="J250" s="2">
-        <v>56936.9625</v>
+        <v>57089.9425</v>
       </c>
       <c r="K250" s="2">
         <v>0</v>
       </c>
       <c r="M250" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N250" s="2">
         <v>0</v>
       </c>
       <c r="O250" t="inlineStr">
         <is>
-          <t>Home to 10th</t>
+          <t>10th to Red Banks to Home</t>
         </is>
       </c>
       <c r="P250" s="2">
-        <v>6.9</v>
+        <v>9.3</v>
       </c>
       <c r="S250" s="2">
-        <v>33.39644</v>
+        <v>56.95536</v>
       </c>
     </row>
     <row r="251">
@@ -15831,20 +15831,20 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>100 East 10th Street</t>
+          <t>Greenville Blvd &amp; Red Banks Rd</t>
         </is>
       </c>
       <c r="D251" s="2">
-        <v>377.84</v>
+        <v>224.86</v>
       </c>
       <c r="E251" s="2">
-        <v>369.84</v>
+        <v>216.86</v>
       </c>
       <c r="F251" s="2">
         <v>7</v>
       </c>
       <c r="G251" s="2">
-        <v>1099</v>
+        <v>105</v>
       </c>
       <c r="H251" t="inlineStr">
         <is>
@@ -15852,7 +15852,7 @@
         </is>
       </c>
       <c r="I251" s="2">
-        <v>52.8342857142857</v>
+        <v>30.98</v>
       </c>
       <c r="J251" s="2">
         <v>57306.8025</v>
@@ -15861,21 +15861,21 @@
         <v>0</v>
       </c>
       <c r="M251" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N251" s="2">
         <v>0</v>
       </c>
       <c r="O251" t="inlineStr">
         <is>
-          <t>10th to Red Banks to Home</t>
+          <t>Home to 10th</t>
         </is>
       </c>
       <c r="P251" s="2">
-        <v>9.3</v>
+        <v>6.9</v>
       </c>
       <c r="S251" s="2">
-        <v>56.95536</v>
+        <v>33.39644</v>
       </c>
     </row>
     <row r="252">
@@ -15902,7 +15902,7 @@
         <v>7</v>
       </c>
       <c r="G252" s="2">
-        <v>1099</v>
+        <v>105</v>
       </c>
       <c r="H252" t="inlineStr">
         <is>
@@ -15947,14 +15947,14 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Greenville Blvd &amp; Red Banks Rd</t>
+          <t>100 East 10th Street</t>
         </is>
       </c>
       <c r="D253" s="2">
-        <v>269.86</v>
+        <v>511.46</v>
       </c>
       <c r="E253" s="2">
-        <v>261.86</v>
+        <v>503.46</v>
       </c>
       <c r="F253" s="2">
         <v>7</v>
@@ -15968,33 +15968,30 @@
         </is>
       </c>
       <c r="I253" s="2">
-        <v>37.4085714285714</v>
+        <v>71.9228571428571</v>
       </c>
       <c r="J253" s="2">
-        <v>57873.4025</v>
+        <v>58115.0025</v>
       </c>
       <c r="K253" s="2">
-        <v>261.86</v>
-      </c>
-      <c r="L253" s="1">
-        <v>46148.000000</v>
+        <v>0</v>
       </c>
       <c r="M253" s="2">
-        <v>0</v>
+        <v>16.88</v>
       </c>
       <c r="N253" s="2">
         <v>0</v>
       </c>
       <c r="O253" t="inlineStr">
         <is>
-          <t>Home to Red Banks</t>
+          <t>Red Banks to 10th Street</t>
         </is>
       </c>
       <c r="P253" s="2">
-        <v>7.5</v>
+        <v>1.9</v>
       </c>
       <c r="S253" s="2">
-        <v>40.32644</v>
+        <v>77.53284</v>
       </c>
     </row>
     <row r="254">
@@ -16008,20 +16005,20 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>100 East 10th Street</t>
+          <t>Greenville Blvd &amp; Red Banks Rd</t>
         </is>
       </c>
       <c r="D254" s="2">
-        <v>511.46</v>
+        <v>269.86</v>
       </c>
       <c r="E254" s="2">
-        <v>503.46</v>
+        <v>261.86</v>
       </c>
       <c r="F254" s="2">
         <v>7</v>
       </c>
       <c r="G254" s="2">
-        <v>1106</v>
+        <v>112</v>
       </c>
       <c r="H254" t="inlineStr">
         <is>
@@ -16029,30 +16026,33 @@
         </is>
       </c>
       <c r="I254" s="2">
-        <v>71.9228571428571</v>
+        <v>37.4085714285714</v>
       </c>
       <c r="J254" s="2">
         <v>58376.8625</v>
       </c>
       <c r="K254" s="2">
-        <v>0</v>
+        <v>261.86</v>
+      </c>
+      <c r="L254" s="1">
+        <v>46148.000000</v>
       </c>
       <c r="M254" s="2">
-        <v>16.88</v>
+        <v>0</v>
       </c>
       <c r="N254" s="2">
         <v>0</v>
       </c>
       <c r="O254" t="inlineStr">
         <is>
-          <t>Red Banks to 10th Street</t>
+          <t>Home to Red Banks</t>
         </is>
       </c>
       <c r="P254" s="2">
-        <v>1.9</v>
+        <v>7.5</v>
       </c>
       <c r="S254" s="2">
-        <v>77.53284</v>
+        <v>40.32644</v>
       </c>
     </row>
     <row r="255">
@@ -16079,7 +16079,7 @@
         <v>7</v>
       </c>
       <c r="G255" s="2">
-        <v>1106</v>
+        <v>112</v>
       </c>
       <c r="H255" t="inlineStr">
         <is>
@@ -16130,14 +16130,14 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Greenville Blvd &amp; Red Banks Rd</t>
+          <t>100 East 10th Street</t>
         </is>
       </c>
       <c r="D256" s="2">
-        <v>263.18</v>
+        <v>400.12</v>
       </c>
       <c r="E256" s="2">
-        <v>255.18</v>
+        <v>392.12</v>
       </c>
       <c r="F256" s="2">
         <v>7</v>
@@ -16151,30 +16151,30 @@
         </is>
       </c>
       <c r="I256" s="2">
-        <v>36.4542857142857</v>
+        <v>56.0171428571429</v>
       </c>
       <c r="J256" s="2">
-        <v>58890.6225</v>
+        <v>59027.5625</v>
       </c>
       <c r="K256" s="2">
         <v>0</v>
       </c>
       <c r="M256" s="2">
-        <v>0</v>
+        <v>9.94</v>
       </c>
       <c r="N256" s="2">
         <v>0</v>
       </c>
       <c r="O256" t="inlineStr">
         <is>
-          <t>Home to Red Banks</t>
+          <t>Red Banks to 10th Street</t>
         </is>
       </c>
       <c r="P256" s="2">
-        <v>7.5</v>
+        <v>1.9</v>
       </c>
       <c r="S256" s="2">
-        <v>39.29772</v>
+        <v>60.38648</v>
       </c>
     </row>
     <row r="257">
@@ -16188,20 +16188,20 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>100 East 10th Street</t>
+          <t>Greenville Blvd &amp; Red Banks Rd</t>
         </is>
       </c>
       <c r="D257" s="2">
-        <v>400.12</v>
+        <v>263.18</v>
       </c>
       <c r="E257" s="2">
-        <v>392.12</v>
+        <v>255.18</v>
       </c>
       <c r="F257" s="2">
         <v>7</v>
       </c>
       <c r="G257" s="2">
-        <v>1113</v>
+        <v>119</v>
       </c>
       <c r="H257" t="inlineStr">
         <is>
@@ -16209,7 +16209,7 @@
         </is>
       </c>
       <c r="I257" s="2">
-        <v>56.0171428571429</v>
+        <v>36.4542857142857</v>
       </c>
       <c r="J257" s="2">
         <v>59282.7425</v>
@@ -16218,21 +16218,21 @@
         <v>0</v>
       </c>
       <c r="M257" s="2">
-        <v>9.94</v>
+        <v>0</v>
       </c>
       <c r="N257" s="2">
         <v>0</v>
       </c>
       <c r="O257" t="inlineStr">
         <is>
-          <t>Red Banks to 10th Street</t>
+          <t>Home to Red Banks</t>
         </is>
       </c>
       <c r="P257" s="2">
-        <v>1.9</v>
+        <v>7.5</v>
       </c>
       <c r="S257" s="2">
-        <v>60.38648</v>
+        <v>39.29772</v>
       </c>
     </row>
     <row r="258">
@@ -16259,7 +16259,7 @@
         <v>7</v>
       </c>
       <c r="G258" s="2">
-        <v>1113</v>
+        <v>119</v>
       </c>
       <c r="H258" t="inlineStr">
         <is>
@@ -16304,14 +16304,14 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Greenville Blvd &amp; Red Banks Rd</t>
+          <t>100 East 10th Street</t>
         </is>
       </c>
       <c r="D259" s="2">
-        <v>181.86</v>
+        <v>478.38</v>
       </c>
       <c r="E259" s="2">
-        <v>173.86</v>
+        <v>470.38</v>
       </c>
       <c r="F259" s="2">
         <v>7</v>
@@ -16325,30 +16325,30 @@
         </is>
       </c>
       <c r="I259" s="2">
-        <v>24.8371428571429</v>
+        <v>67.1971428571429</v>
       </c>
       <c r="J259" s="2">
-        <v>59796.8825</v>
+        <v>60093.4025</v>
       </c>
       <c r="K259" s="2">
         <v>0</v>
       </c>
       <c r="M259" s="2">
-        <v>0</v>
+        <v>12.94</v>
       </c>
       <c r="N259" s="2">
         <v>0</v>
       </c>
       <c r="O259" t="inlineStr">
         <is>
-          <t>Home to Red Banks</t>
+          <t>Red Banks to 10th Street</t>
         </is>
       </c>
       <c r="P259" s="2">
-        <v>7.5</v>
+        <v>1.9</v>
       </c>
       <c r="S259" s="2">
-        <v>26.77444</v>
+        <v>72.43852</v>
       </c>
     </row>
     <row r="260">
@@ -16362,20 +16362,20 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>100 East 10th Street</t>
+          <t>Greenville Blvd &amp; Red Banks Rd</t>
         </is>
       </c>
       <c r="D260" s="2">
-        <v>478.38</v>
+        <v>181.86</v>
       </c>
       <c r="E260" s="2">
-        <v>470.38</v>
+        <v>173.86</v>
       </c>
       <c r="F260" s="2">
         <v>7</v>
       </c>
       <c r="G260" s="2">
-        <v>1120</v>
+        <v>126</v>
       </c>
       <c r="H260" t="inlineStr">
         <is>
@@ -16383,7 +16383,7 @@
         </is>
       </c>
       <c r="I260" s="2">
-        <v>67.1971428571429</v>
+        <v>24.8371428571429</v>
       </c>
       <c r="J260" s="2">
         <v>60267.2625</v>
@@ -16392,21 +16392,21 @@
         <v>0</v>
       </c>
       <c r="M260" s="2">
-        <v>12.94</v>
+        <v>0</v>
       </c>
       <c r="N260" s="2">
         <v>0</v>
       </c>
       <c r="O260" t="inlineStr">
         <is>
-          <t>Red Banks to 10th Street</t>
+          <t>Home to Red Banks</t>
         </is>
       </c>
       <c r="P260" s="2">
-        <v>1.9</v>
+        <v>7.5</v>
       </c>
       <c r="S260" s="2">
-        <v>72.43852</v>
+        <v>26.77444</v>
       </c>
     </row>
     <row r="261">
@@ -16433,7 +16433,7 @@
         <v>7</v>
       </c>
       <c r="G261" s="2">
-        <v>1120</v>
+        <v>126</v>
       </c>
       <c r="H261" t="inlineStr">
         <is>
@@ -16481,14 +16481,14 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Greenville Blvd &amp; Red Banks Rd</t>
+          <t>100 East 10th Street</t>
         </is>
       </c>
       <c r="D262" s="2">
-        <v>225</v>
+        <v>376.66</v>
       </c>
       <c r="E262" s="2">
-        <v>217</v>
+        <v>368.66</v>
       </c>
       <c r="F262" s="2">
         <v>7</v>
@@ -16502,30 +16502,30 @@
         </is>
       </c>
       <c r="I262" s="2">
-        <v>31</v>
+        <v>52.6657142857143</v>
       </c>
       <c r="J262" s="2">
-        <v>60703.4825</v>
+        <v>60855.1425</v>
       </c>
       <c r="K262" s="2">
         <v>0</v>
       </c>
       <c r="M262" s="2">
-        <v>0</v>
+        <v>8.76</v>
       </c>
       <c r="N262" s="2">
         <v>0</v>
       </c>
       <c r="O262" t="inlineStr">
         <is>
-          <t>Home to Red Banks</t>
+          <t>Red Banks to 10th Street</t>
         </is>
       </c>
       <c r="P262" s="2">
-        <v>7.5</v>
+        <v>1.9</v>
       </c>
       <c r="S262" s="2">
-        <v>33.418</v>
+        <v>56.77364</v>
       </c>
     </row>
     <row r="263">
@@ -16539,20 +16539,20 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>100 East 10th Street</t>
+          <t>Greenville Blvd &amp; Red Banks Rd</t>
         </is>
       </c>
       <c r="D263" s="2">
-        <v>376.66</v>
+        <v>225</v>
       </c>
       <c r="E263" s="2">
-        <v>368.66</v>
+        <v>217</v>
       </c>
       <c r="F263" s="2">
         <v>7</v>
       </c>
       <c r="G263" s="2">
-        <v>1127</v>
+        <v>133</v>
       </c>
       <c r="H263" t="inlineStr">
         <is>
@@ -16560,7 +16560,7 @@
         </is>
       </c>
       <c r="I263" s="2">
-        <v>52.6657142857143</v>
+        <v>31</v>
       </c>
       <c r="J263" s="2">
         <v>61072.1425</v>
@@ -16569,21 +16569,21 @@
         <v>0</v>
       </c>
       <c r="M263" s="2">
-        <v>8.76</v>
+        <v>0</v>
       </c>
       <c r="N263" s="2">
         <v>0</v>
       </c>
       <c r="O263" t="inlineStr">
         <is>
-          <t>Red Banks to 10th Street</t>
+          <t>Home to Red Banks</t>
         </is>
       </c>
       <c r="P263" s="2">
-        <v>1.9</v>
+        <v>7.5</v>
       </c>
       <c r="S263" s="2">
-        <v>56.77364</v>
+        <v>33.418</v>
       </c>
     </row>
     <row r="264">
@@ -16610,7 +16610,7 @@
         <v>7</v>
       </c>
       <c r="G264" s="2">
-        <v>1127</v>
+        <v>133</v>
       </c>
       <c r="H264" t="inlineStr">
         <is>
@@ -16655,14 +16655,14 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Greenville Blvd &amp; Red Banks Rd</t>
+          <t>100 East 10th Street</t>
         </is>
       </c>
       <c r="D265" s="2">
-        <v>221.3</v>
+        <v>321.16</v>
       </c>
       <c r="E265" s="2">
-        <v>213.3</v>
+        <v>313.16</v>
       </c>
       <c r="F265" s="2">
         <v>7</v>
@@ -16676,10 +16676,10 @@
         </is>
       </c>
       <c r="I265" s="2">
-        <v>30.4714285714286</v>
+        <v>44.7371428571429</v>
       </c>
       <c r="J265" s="2">
-        <v>61619.3725</v>
+        <v>61719.2325</v>
       </c>
       <c r="K265" s="2">
         <v>0</v>
@@ -16692,14 +16692,14 @@
       </c>
       <c r="O265" t="inlineStr">
         <is>
-          <t>Home to Red Banks</t>
+          <t>Red Banks to 10th Street</t>
         </is>
       </c>
       <c r="P265" s="2">
-        <v>7.5</v>
+        <v>1.9</v>
       </c>
       <c r="S265" s="2">
-        <v>32.8482</v>
+        <v>48.22664</v>
       </c>
     </row>
     <row r="266">
@@ -16713,20 +16713,20 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>100 East 10th Street</t>
+          <t>Greenville Blvd &amp; Red Banks Rd</t>
         </is>
       </c>
       <c r="D266" s="2">
-        <v>321.16</v>
+        <v>221.3</v>
       </c>
       <c r="E266" s="2">
-        <v>313.16</v>
+        <v>213.3</v>
       </c>
       <c r="F266" s="2">
         <v>7</v>
       </c>
       <c r="G266" s="2">
-        <v>1134</v>
+        <v>140</v>
       </c>
       <c r="H266" t="inlineStr">
         <is>
@@ -16734,7 +16734,7 @@
         </is>
       </c>
       <c r="I266" s="2">
-        <v>44.7371428571429</v>
+        <v>30.4714285714286</v>
       </c>
       <c r="J266" s="2">
         <v>61932.5325</v>
@@ -16750,14 +16750,14 @@
       </c>
       <c r="O266" t="inlineStr">
         <is>
-          <t>Red Banks to 10th Street</t>
+          <t>Home to Red Banks</t>
         </is>
       </c>
       <c r="P266" s="2">
-        <v>1.9</v>
+        <v>7.5</v>
       </c>
       <c r="S266" s="2">
-        <v>48.22664</v>
+        <v>32.8482</v>
       </c>
     </row>
     <row r="267">
@@ -16784,7 +16784,7 @@
         <v>7</v>
       </c>
       <c r="G267" s="2">
-        <v>1134</v>
+        <v>140</v>
       </c>
       <c r="H267" t="inlineStr">
         <is>
@@ -16829,14 +16829,14 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Stanton Sq &amp; Arlington Dr</t>
+          <t>100 East 10th Street</t>
         </is>
       </c>
       <c r="D268" s="2">
-        <v>381.46</v>
+        <v>310.86</v>
       </c>
       <c r="E268" s="2">
-        <v>373.46</v>
+        <v>302.86</v>
       </c>
       <c r="F268" s="2">
         <v>8</v>
@@ -16850,30 +16850,30 @@
         </is>
       </c>
       <c r="I268" s="2">
-        <v>46.6825</v>
+        <v>37.8575</v>
       </c>
       <c r="J268" s="2">
-        <v>62592.7525</v>
+        <v>62522.1525</v>
       </c>
       <c r="K268" s="2">
         <v>0</v>
       </c>
       <c r="M268" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N268" s="2">
         <v>0</v>
       </c>
       <c r="O268" t="inlineStr">
         <is>
-          <t>10th St to Stanton to Home</t>
+          <t>Red Banks to 10th Street</t>
         </is>
       </c>
       <c r="P268" s="2">
-        <v>13.7</v>
+        <v>1.9</v>
       </c>
       <c r="S268" s="2">
-        <v>57.51284</v>
+        <v>46.64044</v>
       </c>
     </row>
     <row r="269">
@@ -16887,20 +16887,20 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>100 East 10th Street</t>
+          <t>Greenville Blvd &amp; Red Banks Rd</t>
         </is>
       </c>
       <c r="D269" s="2">
-        <v>310.86</v>
+        <v>211.82</v>
       </c>
       <c r="E269" s="2">
-        <v>302.86</v>
+        <v>203.82</v>
       </c>
       <c r="F269" s="2">
         <v>8</v>
       </c>
       <c r="G269" s="2">
-        <v>1142</v>
+        <v>148</v>
       </c>
       <c r="H269" t="inlineStr">
         <is>
@@ -16908,10 +16908,10 @@
         </is>
       </c>
       <c r="I269" s="2">
-        <v>37.8575</v>
+        <v>25.4775</v>
       </c>
       <c r="J269" s="2">
-        <v>62895.6125</v>
+        <v>62725.9725</v>
       </c>
       <c r="K269" s="2">
         <v>0</v>
@@ -16924,14 +16924,14 @@
       </c>
       <c r="O269" t="inlineStr">
         <is>
-          <t>Red Banks to 10th Street</t>
+          <t>Home to Red Banks</t>
         </is>
       </c>
       <c r="P269" s="2">
-        <v>1.9</v>
+        <v>7.5</v>
       </c>
       <c r="S269" s="2">
-        <v>46.64044</v>
+        <v>31.38828</v>
       </c>
     </row>
     <row r="270">
@@ -16945,20 +16945,20 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Greenville Blvd &amp; Red Banks Rd</t>
+          <t>Stanton Sq &amp; Arlington Dr</t>
         </is>
       </c>
       <c r="D270" s="2">
-        <v>211.82</v>
+        <v>381.46</v>
       </c>
       <c r="E270" s="2">
-        <v>203.82</v>
+        <v>373.46</v>
       </c>
       <c r="F270" s="2">
         <v>8</v>
       </c>
       <c r="G270" s="2">
-        <v>1142</v>
+        <v>148</v>
       </c>
       <c r="H270" t="inlineStr">
         <is>
@@ -16966,7 +16966,7 @@
         </is>
       </c>
       <c r="I270" s="2">
-        <v>25.4775</v>
+        <v>46.6825</v>
       </c>
       <c r="J270" s="2">
         <v>63099.4325</v>
@@ -16975,21 +16975,21 @@
         <v>0</v>
       </c>
       <c r="M270" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N270" s="2">
         <v>0</v>
       </c>
       <c r="O270" t="inlineStr">
         <is>
-          <t>Home to Red Banks</t>
+          <t>10th St to Stanton to Home</t>
         </is>
       </c>
       <c r="P270" s="2">
-        <v>7.5</v>
+        <v>13.7</v>
       </c>
       <c r="S270" s="2">
-        <v>31.38828</v>
+        <v>57.51284</v>
       </c>
     </row>
     <row r="271">
@@ -17003,14 +17003,14 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Winterville</t>
+          <t>100 East 10th Street</t>
         </is>
       </c>
       <c r="D271" s="2">
-        <v>173.34</v>
+        <v>321.12</v>
       </c>
       <c r="E271" s="2">
-        <v>165.34</v>
+        <v>305.12</v>
       </c>
       <c r="F271" s="2">
         <v>7</v>
@@ -17024,38 +17024,33 @@
         </is>
       </c>
       <c r="I271" s="2">
-        <v>23.62</v>
+        <v>43.5885714285714</v>
       </c>
       <c r="J271" s="2">
-        <v>63264.7725</v>
+        <v>63404.5525</v>
       </c>
       <c r="K271" s="2">
-        <v>165.34</v>
+        <v>102.62</v>
       </c>
       <c r="L271" s="1">
         <v>46193.000000</v>
       </c>
       <c r="M271" s="2">
-        <v>0</v>
+        <v>11.42</v>
       </c>
       <c r="N271" s="2">
         <v>0</v>
       </c>
       <c r="O271" t="inlineStr">
         <is>
-          <t>Home to Winterville (Bypass)</t>
+          <t>Home to 10th</t>
         </is>
       </c>
       <c r="P271" s="2">
-        <v>19.1</v>
-      </c>
-      <c r="R271" t="inlineStr">
-        <is>
-          <t>1st Winterville Collection! Welcome to the team!</t>
-        </is>
+        <v>6.9</v>
       </c>
       <c r="S271" s="2">
-        <v>25.46236</v>
+        <v>46.98848</v>
       </c>
     </row>
     <row r="272">
@@ -17082,7 +17077,7 @@
         <v>7</v>
       </c>
       <c r="G272" s="2">
-        <v>1149</v>
+        <v>155</v>
       </c>
       <c r="H272" t="inlineStr">
         <is>
@@ -17093,7 +17088,7 @@
         <v>26.6971428571429</v>
       </c>
       <c r="J272" s="2">
-        <v>63451.6525</v>
+        <v>63591.4325</v>
       </c>
       <c r="K272" s="2">
         <v>186.88</v>
@@ -17130,20 +17125,20 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>100 East 10th Street</t>
+          <t>Stanton Sq &amp; Arlington Dr</t>
         </is>
       </c>
       <c r="D273" s="2">
-        <v>321.12</v>
+        <v>385.68</v>
       </c>
       <c r="E273" s="2">
-        <v>305.12</v>
+        <v>369.68</v>
       </c>
       <c r="F273" s="2">
         <v>7</v>
       </c>
       <c r="G273" s="2">
-        <v>1149</v>
+        <v>155</v>
       </c>
       <c r="H273" t="inlineStr">
         <is>
@@ -17151,33 +17146,33 @@
         </is>
       </c>
       <c r="I273" s="2">
-        <v>43.5885714285714</v>
+        <v>52.8114285714286</v>
       </c>
       <c r="J273" s="2">
-        <v>63756.7725</v>
+        <v>63961.1125</v>
       </c>
       <c r="K273" s="2">
-        <v>102.62</v>
+        <v>146.28</v>
       </c>
       <c r="L273" s="1">
         <v>46193.000000</v>
       </c>
       <c r="M273" s="2">
-        <v>11.42</v>
+        <v>0</v>
       </c>
       <c r="N273" s="2">
         <v>0</v>
       </c>
       <c r="O273" t="inlineStr">
         <is>
-          <t>Home to 10th</t>
+          <t>10th St to Stanton to Home</t>
         </is>
       </c>
       <c r="P273" s="2">
-        <v>6.9</v>
+        <v>13.7</v>
       </c>
       <c r="S273" s="2">
-        <v>46.98848</v>
+        <v>56.93072</v>
       </c>
     </row>
     <row r="274">
@@ -17191,20 +17186,20 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Stanton Sq &amp; Arlington Dr</t>
+          <t>Winterville</t>
         </is>
       </c>
       <c r="D274" s="2">
-        <v>385.68</v>
+        <v>173.34</v>
       </c>
       <c r="E274" s="2">
-        <v>369.68</v>
+        <v>165.34</v>
       </c>
       <c r="F274" s="2">
         <v>7</v>
       </c>
       <c r="G274" s="2">
-        <v>1149</v>
+        <v>0</v>
       </c>
       <c r="H274" t="inlineStr">
         <is>
@@ -17212,13 +17207,13 @@
         </is>
       </c>
       <c r="I274" s="2">
-        <v>52.8114285714286</v>
+        <v>23.62</v>
       </c>
       <c r="J274" s="2">
         <v>64126.4525</v>
       </c>
       <c r="K274" s="2">
-        <v>146.28</v>
+        <v>165.34</v>
       </c>
       <c r="L274" s="1">
         <v>46193.000000</v>
@@ -17231,14 +17226,19 @@
       </c>
       <c r="O274" t="inlineStr">
         <is>
-          <t>10th St to Stanton to Home</t>
+          <t>Home to Winterville (Bypass)</t>
         </is>
       </c>
       <c r="P274" s="2">
-        <v>13.7</v>
+        <v>19.1</v>
+      </c>
+      <c r="R274" t="inlineStr">
+        <is>
+          <t>1st Winterville Collection! Welcome to the team!</t>
+        </is>
       </c>
       <c r="S274" s="2">
-        <v>56.93072</v>
+        <v>25.46236</v>
       </c>
     </row>
     <row r="275">
@@ -17252,14 +17252,14 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Winterville</t>
+          <t>100 East 10th Street</t>
         </is>
       </c>
       <c r="D275" s="2">
-        <v>197.38</v>
+        <v>321.78</v>
       </c>
       <c r="E275" s="2">
-        <v>189.38</v>
+        <v>305.78</v>
       </c>
       <c r="F275" s="2">
         <v>6</v>
@@ -17273,10 +17273,10 @@
         </is>
       </c>
       <c r="I275" s="2">
-        <v>31.5633333333333</v>
+        <v>50.9633333333333</v>
       </c>
       <c r="J275" s="2">
-        <v>64315.8325</v>
+        <v>64432.2325</v>
       </c>
       <c r="K275" s="2">
         <v>0</v>
@@ -17289,14 +17289,14 @@
       </c>
       <c r="O275" t="inlineStr">
         <is>
-          <t>Home to Winterville (Bypass)</t>
+          <t>Home to 10th</t>
         </is>
       </c>
       <c r="P275" s="2">
-        <v>19.1</v>
+        <v>6.9</v>
       </c>
       <c r="S275" s="2">
-        <v>29.16452</v>
+        <v>47.09012</v>
       </c>
     </row>
     <row r="276">
@@ -17323,7 +17323,7 @@
         <v>6</v>
       </c>
       <c r="G276" s="2">
-        <v>1155</v>
+        <v>161</v>
       </c>
       <c r="H276" t="inlineStr">
         <is>
@@ -17334,7 +17334,7 @@
         <v>21.8433333333333</v>
       </c>
       <c r="J276" s="2">
-        <v>64446.8925</v>
+        <v>64563.2925</v>
       </c>
       <c r="K276" s="2">
         <v>0</v>
@@ -17368,20 +17368,20 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>100 East 10th Street</t>
+          <t>Stanton Sq &amp; Arlington Dr</t>
         </is>
       </c>
       <c r="D277" s="2">
-        <v>321.78</v>
+        <v>286.3</v>
       </c>
       <c r="E277" s="2">
-        <v>305.78</v>
+        <v>270.3</v>
       </c>
       <c r="F277" s="2">
         <v>6</v>
       </c>
       <c r="G277" s="2">
-        <v>1155</v>
+        <v>161</v>
       </c>
       <c r="H277" t="inlineStr">
         <is>
@@ -17389,10 +17389,10 @@
         </is>
       </c>
       <c r="I277" s="2">
-        <v>50.9633333333333</v>
+        <v>45.05</v>
       </c>
       <c r="J277" s="2">
-        <v>64752.6725</v>
+        <v>64833.5925</v>
       </c>
       <c r="K277" s="2">
         <v>0</v>
@@ -17405,14 +17405,14 @@
       </c>
       <c r="O277" t="inlineStr">
         <is>
-          <t>Home to 10th</t>
+          <t>10th St to Stanton to Home</t>
         </is>
       </c>
       <c r="P277" s="2">
-        <v>6.9</v>
+        <v>13.7</v>
       </c>
       <c r="S277" s="2">
-        <v>47.09012</v>
+        <v>41.6262</v>
       </c>
     </row>
     <row r="278">
@@ -17426,20 +17426,20 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Stanton Sq &amp; Arlington Dr</t>
+          <t>Winterville</t>
         </is>
       </c>
       <c r="D278" s="2">
-        <v>286.3</v>
+        <v>197.38</v>
       </c>
       <c r="E278" s="2">
-        <v>270.3</v>
+        <v>189.38</v>
       </c>
       <c r="F278" s="2">
         <v>6</v>
       </c>
       <c r="G278" s="2">
-        <v>1155</v>
+        <v>6</v>
       </c>
       <c r="H278" t="inlineStr">
         <is>
@@ -17447,7 +17447,7 @@
         </is>
       </c>
       <c r="I278" s="2">
-        <v>45.05</v>
+        <v>31.5633333333333</v>
       </c>
       <c r="J278" s="2">
         <v>65022.9725</v>
@@ -17463,14 +17463,14 @@
       </c>
       <c r="O278" t="inlineStr">
         <is>
-          <t>10th St to Stanton to Home</t>
+          <t>Home to Winterville (Bypass)</t>
         </is>
       </c>
       <c r="P278" s="2">
-        <v>13.7</v>
+        <v>19.1</v>
       </c>
       <c r="S278" s="2">
-        <v>41.6262</v>
+        <v>29.16452</v>
       </c>
     </row>
     <row r="279">
@@ -17484,14 +17484,14 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Winterville</t>
+          <t>100 East 10th Street</t>
         </is>
       </c>
       <c r="D279" s="2">
-        <v>260.46</v>
+        <v>219.84</v>
       </c>
       <c r="E279" s="2">
-        <v>244.46</v>
+        <v>211.84</v>
       </c>
       <c r="F279" s="2">
         <v>7</v>
@@ -17505,30 +17505,30 @@
         </is>
       </c>
       <c r="I279" s="2">
-        <v>34.9228571428571</v>
+        <v>30.2628571428571</v>
       </c>
       <c r="J279" s="2">
-        <v>65267.4325</v>
+        <v>65234.8125</v>
       </c>
       <c r="K279" s="2">
         <v>0</v>
       </c>
       <c r="M279" s="2">
-        <v>0</v>
+        <v>5.66</v>
       </c>
       <c r="N279" s="2">
         <v>0</v>
       </c>
       <c r="O279" t="inlineStr">
         <is>
-          <t>Home to Winterville (Bypass)</t>
+          <t>Home to 10th</t>
         </is>
       </c>
       <c r="P279" s="2">
-        <v>19.1</v>
+        <v>6.9</v>
       </c>
       <c r="S279" s="2">
-        <v>37.64684</v>
+        <v>32.62336</v>
       </c>
     </row>
     <row r="280">
@@ -17555,7 +17555,7 @@
         <v>7</v>
       </c>
       <c r="G280" s="2">
-        <v>1162</v>
+        <v>168</v>
       </c>
       <c r="H280" t="inlineStr">
         <is>
@@ -17566,7 +17566,7 @@
         <v>39.8657142857143</v>
       </c>
       <c r="J280" s="2">
-        <v>65546.4925</v>
+        <v>65513.8725</v>
       </c>
       <c r="K280" s="2">
         <v>0</v>
@@ -17600,20 +17600,20 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>100 East 10th Street</t>
+          <t>Stanton Sq &amp; Arlington Dr</t>
         </is>
       </c>
       <c r="D281" s="2">
-        <v>219.84</v>
+        <v>365.42</v>
       </c>
       <c r="E281" s="2">
-        <v>211.84</v>
+        <v>349.42</v>
       </c>
       <c r="F281" s="2">
         <v>7</v>
       </c>
       <c r="G281" s="2">
-        <v>1162</v>
+        <v>168</v>
       </c>
       <c r="H281" t="inlineStr">
         <is>
@@ -17621,30 +17621,30 @@
         </is>
       </c>
       <c r="I281" s="2">
-        <v>30.2628571428571</v>
+        <v>49.9171428571429</v>
       </c>
       <c r="J281" s="2">
-        <v>65758.3325</v>
+        <v>65863.2925</v>
       </c>
       <c r="K281" s="2">
         <v>0</v>
       </c>
       <c r="M281" s="2">
-        <v>5.66</v>
+        <v>0</v>
       </c>
       <c r="N281" s="2">
         <v>0</v>
       </c>
       <c r="O281" t="inlineStr">
         <is>
-          <t>Home to 10th</t>
+          <t>10th St to Stanton to Home</t>
         </is>
       </c>
       <c r="P281" s="2">
-        <v>6.9</v>
+        <v>13.7</v>
       </c>
       <c r="S281" s="2">
-        <v>32.62336</v>
+        <v>53.81068</v>
       </c>
     </row>
     <row r="282">
@@ -17658,20 +17658,20 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Stanton Sq &amp; Arlington Dr</t>
+          <t>Winterville</t>
         </is>
       </c>
       <c r="D282" s="2">
-        <v>365.42</v>
+        <v>260.46</v>
       </c>
       <c r="E282" s="2">
-        <v>349.42</v>
+        <v>244.46</v>
       </c>
       <c r="F282" s="2">
         <v>7</v>
       </c>
       <c r="G282" s="2">
-        <v>1162</v>
+        <v>13</v>
       </c>
       <c r="H282" t="inlineStr">
         <is>
@@ -17679,7 +17679,7 @@
         </is>
       </c>
       <c r="I282" s="2">
-        <v>49.9171428571429</v>
+        <v>34.9228571428571</v>
       </c>
       <c r="J282" s="2">
         <v>66107.7525</v>
@@ -17695,14 +17695,14 @@
       </c>
       <c r="O282" t="inlineStr">
         <is>
-          <t>10th St to Stanton to Home</t>
+          <t>Home to Winterville (Bypass)</t>
         </is>
       </c>
       <c r="P282" s="2">
-        <v>13.7</v>
+        <v>19.1</v>
       </c>
       <c r="S282" s="2">
-        <v>53.81068</v>
+        <v>37.64684</v>
       </c>
     </row>
     <row r="283">
@@ -17716,14 +17716,14 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Winterville</t>
+          <t>100 East 10th Street</t>
         </is>
       </c>
       <c r="D283" s="2">
-        <v>174.58</v>
+        <v>333.56</v>
       </c>
       <c r="E283" s="2">
-        <v>166.58</v>
+        <v>317.56</v>
       </c>
       <c r="F283" s="2">
         <v>7</v>
@@ -17737,30 +17737,30 @@
         </is>
       </c>
       <c r="I283" s="2">
-        <v>23.7971428571429</v>
+        <v>45.3657142857143</v>
       </c>
       <c r="J283" s="2">
-        <v>66274.3325</v>
+        <v>66425.3125</v>
       </c>
       <c r="K283" s="2">
         <v>0</v>
       </c>
       <c r="M283" s="2">
-        <v>13.84</v>
+        <v>0</v>
       </c>
       <c r="N283" s="2">
         <v>0</v>
       </c>
       <c r="O283" t="inlineStr">
         <is>
-          <t>Home to Winterville (Bypass)</t>
+          <t>Home to 10th</t>
         </is>
       </c>
       <c r="P283" s="2">
-        <v>19.1</v>
+        <v>6.9</v>
       </c>
       <c r="S283" s="2">
-        <v>25.65332</v>
+        <v>48.90424</v>
       </c>
     </row>
     <row r="284">
@@ -17787,7 +17787,7 @@
         <v>7</v>
       </c>
       <c r="G284" s="2">
-        <v>1169</v>
+        <v>175</v>
       </c>
       <c r="H284" t="inlineStr">
         <is>
@@ -17798,7 +17798,7 @@
         <v>12.7542857142857</v>
       </c>
       <c r="J284" s="2">
-        <v>66363.6125</v>
+        <v>66514.5925</v>
       </c>
       <c r="K284" s="2">
         <v>0</v>
@@ -17832,20 +17832,20 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>100 East 10th Street</t>
+          <t>Stanton Sq &amp; Arlington Dr</t>
         </is>
       </c>
       <c r="D285" s="2">
-        <v>333.56</v>
+        <v>356.94</v>
       </c>
       <c r="E285" s="2">
-        <v>317.56</v>
+        <v>340.94</v>
       </c>
       <c r="F285" s="2">
         <v>7</v>
       </c>
       <c r="G285" s="2">
-        <v>1169</v>
+        <v>175</v>
       </c>
       <c r="H285" t="inlineStr">
         <is>
@@ -17853,10 +17853,10 @@
         </is>
       </c>
       <c r="I285" s="2">
-        <v>45.3657142857143</v>
+        <v>48.7057142857143</v>
       </c>
       <c r="J285" s="2">
-        <v>66681.1725</v>
+        <v>66855.5325</v>
       </c>
       <c r="K285" s="2">
         <v>0</v>
@@ -17869,14 +17869,14 @@
       </c>
       <c r="O285" t="inlineStr">
         <is>
-          <t>Home to 10th</t>
+          <t>10th St to Stanton to Home</t>
         </is>
       </c>
       <c r="P285" s="2">
-        <v>6.9</v>
+        <v>13.7</v>
       </c>
       <c r="S285" s="2">
-        <v>48.90424</v>
+        <v>52.50476</v>
       </c>
     </row>
     <row r="286">
@@ -17890,20 +17890,20 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Stanton Sq &amp; Arlington Dr</t>
+          <t>Winterville</t>
         </is>
       </c>
       <c r="D286" s="2">
-        <v>356.94</v>
+        <v>174.58</v>
       </c>
       <c r="E286" s="2">
-        <v>340.94</v>
+        <v>166.58</v>
       </c>
       <c r="F286" s="2">
         <v>7</v>
       </c>
       <c r="G286" s="2">
-        <v>1169</v>
+        <v>20</v>
       </c>
       <c r="H286" t="inlineStr">
         <is>
@@ -17911,7 +17911,7 @@
         </is>
       </c>
       <c r="I286" s="2">
-        <v>48.7057142857143</v>
+        <v>23.7971428571429</v>
       </c>
       <c r="J286" s="2">
         <v>67022.1125</v>
@@ -17920,21 +17920,21 @@
         <v>0</v>
       </c>
       <c r="M286" s="2">
-        <v>0</v>
+        <v>13.84</v>
       </c>
       <c r="N286" s="2">
         <v>0</v>
       </c>
       <c r="O286" t="inlineStr">
         <is>
-          <t>10th St to Stanton to Home</t>
+          <t>Home to Winterville (Bypass)</t>
         </is>
       </c>
       <c r="P286" s="2">
-        <v>13.7</v>
+        <v>19.1</v>
       </c>
       <c r="S286" s="2">
-        <v>52.50476</v>
+        <v>25.65332</v>
       </c>
     </row>
     <row r="287">
@@ -17948,14 +17948,14 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Winterville</t>
+          <t>100 East 10th Street</t>
         </is>
       </c>
       <c r="D287" s="2">
-        <v>197.26</v>
+        <v>436.62</v>
       </c>
       <c r="E287" s="2">
-        <v>189.26</v>
+        <v>412.62</v>
       </c>
       <c r="F287" s="2">
         <v>8</v>
@@ -17969,10 +17969,10 @@
         </is>
       </c>
       <c r="I287" s="2">
-        <v>23.6575</v>
+        <v>51.5775</v>
       </c>
       <c r="J287" s="2">
-        <v>67211.3725</v>
+        <v>67434.7325</v>
       </c>
       <c r="K287" s="2">
         <v>0</v>
@@ -17985,14 +17985,14 @@
       </c>
       <c r="O287" t="inlineStr">
         <is>
-          <t>Home to Winterville (Bypass)</t>
+          <t>Home to 10th</t>
         </is>
       </c>
       <c r="P287" s="2">
-        <v>19.1</v>
+        <v>6.9</v>
       </c>
       <c r="S287" s="2">
-        <v>29.14604</v>
+        <v>63.54348</v>
       </c>
     </row>
     <row r="288">
@@ -18019,7 +18019,7 @@
         <v>8</v>
       </c>
       <c r="G288" s="2">
-        <v>1177</v>
+        <v>183</v>
       </c>
       <c r="H288" t="inlineStr">
         <is>
@@ -18030,7 +18030,7 @@
         <v>25.5375</v>
       </c>
       <c r="J288" s="2">
-        <v>67415.6725</v>
+        <v>67639.0325</v>
       </c>
       <c r="K288" s="2">
         <v>0</v>
@@ -18064,20 +18064,20 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>100 East 10th Street</t>
+          <t>Stanton Sq &amp; Arlington Dr</t>
         </is>
       </c>
       <c r="D289" s="2">
-        <v>436.62</v>
+        <v>410.98</v>
       </c>
       <c r="E289" s="2">
-        <v>412.62</v>
+        <v>394.98</v>
       </c>
       <c r="F289" s="2">
         <v>8</v>
       </c>
       <c r="G289" s="2">
-        <v>1177</v>
+        <v>183</v>
       </c>
       <c r="H289" t="inlineStr">
         <is>
@@ -18085,10 +18085,10 @@
         </is>
       </c>
       <c r="I289" s="2">
-        <v>51.5775</v>
+        <v>49.3725</v>
       </c>
       <c r="J289" s="2">
-        <v>67828.2925</v>
+        <v>68034.0125</v>
       </c>
       <c r="K289" s="2">
         <v>0</v>
@@ -18101,14 +18101,14 @@
       </c>
       <c r="O289" t="inlineStr">
         <is>
-          <t>Home to 10th</t>
+          <t>10th St to Stanton to Home</t>
         </is>
       </c>
       <c r="P289" s="2">
-        <v>6.9</v>
+        <v>13.7</v>
       </c>
       <c r="S289" s="2">
-        <v>63.54348</v>
+        <v>60.82692</v>
       </c>
     </row>
     <row r="290">
@@ -18122,20 +18122,20 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Stanton Sq &amp; Arlington Dr</t>
+          <t>Winterville</t>
         </is>
       </c>
       <c r="D290" s="2">
-        <v>410.98</v>
+        <v>197.26</v>
       </c>
       <c r="E290" s="2">
-        <v>394.98</v>
+        <v>189.26</v>
       </c>
       <c r="F290" s="2">
         <v>8</v>
       </c>
       <c r="G290" s="2">
-        <v>1177</v>
+        <v>28</v>
       </c>
       <c r="H290" t="inlineStr">
         <is>
@@ -18143,7 +18143,7 @@
         </is>
       </c>
       <c r="I290" s="2">
-        <v>49.3725</v>
+        <v>23.6575</v>
       </c>
       <c r="J290" s="2">
         <v>68223.2725</v>
@@ -18159,14 +18159,14 @@
       </c>
       <c r="O290" t="inlineStr">
         <is>
-          <t>10th St to Stanton to Home</t>
+          <t>Home to Winterville (Bypass)</t>
         </is>
       </c>
       <c r="P290" s="2">
-        <v>13.7</v>
+        <v>19.1</v>
       </c>
       <c r="S290" s="2">
-        <v>60.82692</v>
+        <v>29.14604</v>
       </c>
     </row>
     <row r="291">
@@ -18180,14 +18180,14 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Winterville</t>
+          <t>100 East 10th Street</t>
         </is>
       </c>
       <c r="D291" s="2">
-        <v>234.38</v>
+        <v>397.4</v>
       </c>
       <c r="E291" s="2">
-        <v>218.38</v>
+        <v>381.4</v>
       </c>
       <c r="F291" s="2">
         <v>7</v>
@@ -18201,10 +18201,10 @@
         </is>
       </c>
       <c r="I291" s="2">
-        <v>31.1971428571429</v>
+        <v>54.4857142857143</v>
       </c>
       <c r="J291" s="2">
-        <v>68441.6525</v>
+        <v>68604.6725</v>
       </c>
       <c r="K291" s="2">
         <v>0</v>
@@ -18217,14 +18217,14 @@
       </c>
       <c r="O291" t="inlineStr">
         <is>
-          <t>Home to Winterville (Arboretum to Memorial)</t>
+          <t>Home to 10th</t>
         </is>
       </c>
       <c r="P291" s="2">
-        <v>10.3</v>
+        <v>6.9</v>
       </c>
       <c r="S291" s="2">
-        <v>33.63052</v>
+        <v>58.7356</v>
       </c>
     </row>
     <row r="292">
@@ -18251,7 +18251,7 @@
         <v>7</v>
       </c>
       <c r="G292" s="2">
-        <v>1184</v>
+        <v>190</v>
       </c>
       <c r="H292" t="inlineStr">
         <is>
@@ -18262,7 +18262,7 @@
         <v>32.7828571428571</v>
       </c>
       <c r="J292" s="2">
-        <v>68671.1325</v>
+        <v>68834.1525</v>
       </c>
       <c r="K292" s="2">
         <v>0</v>
@@ -18296,20 +18296,20 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>100 East 10th Street</t>
+          <t>Stanton Sq &amp; Arlington Dr</t>
         </is>
       </c>
       <c r="D293" s="2">
-        <v>397.4</v>
+        <v>404.62</v>
       </c>
       <c r="E293" s="2">
-        <v>381.4</v>
+        <v>388.62</v>
       </c>
       <c r="F293" s="2">
         <v>7</v>
       </c>
       <c r="G293" s="2">
-        <v>1184</v>
+        <v>190</v>
       </c>
       <c r="H293" t="inlineStr">
         <is>
@@ -18317,10 +18317,10 @@
         </is>
       </c>
       <c r="I293" s="2">
-        <v>54.4857142857143</v>
+        <v>55.5171428571429</v>
       </c>
       <c r="J293" s="2">
-        <v>69052.5325</v>
+        <v>69222.7725</v>
       </c>
       <c r="K293" s="2">
         <v>0</v>
@@ -18333,14 +18333,14 @@
       </c>
       <c r="O293" t="inlineStr">
         <is>
-          <t>Home to 10th</t>
+          <t>10th St to Stanton to Home</t>
         </is>
       </c>
       <c r="P293" s="2">
-        <v>6.9</v>
+        <v>13.7</v>
       </c>
       <c r="S293" s="2">
-        <v>58.7356</v>
+        <v>59.84748</v>
       </c>
     </row>
     <row r="294">
@@ -18354,20 +18354,20 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Stanton Sq &amp; Arlington Dr</t>
+          <t>Winterville</t>
         </is>
       </c>
       <c r="D294" s="2">
-        <v>404.62</v>
+        <v>234.38</v>
       </c>
       <c r="E294" s="2">
-        <v>388.62</v>
+        <v>218.38</v>
       </c>
       <c r="F294" s="2">
         <v>7</v>
       </c>
       <c r="G294" s="2">
-        <v>1184</v>
+        <v>35</v>
       </c>
       <c r="H294" t="inlineStr">
         <is>
@@ -18375,7 +18375,7 @@
         </is>
       </c>
       <c r="I294" s="2">
-        <v>55.5171428571429</v>
+        <v>31.1971428571429</v>
       </c>
       <c r="J294" s="2">
         <v>69441.1525</v>
@@ -18391,14 +18391,14 @@
       </c>
       <c r="O294" t="inlineStr">
         <is>
-          <t>10th St to Stanton to Home</t>
+          <t>Home to Winterville (Arboretum to Memorial)</t>
         </is>
       </c>
       <c r="P294" s="2">
-        <v>13.7</v>
+        <v>10.3</v>
       </c>
       <c r="S294" s="2">
-        <v>59.84748</v>
+        <v>33.63052</v>
       </c>
     </row>
     <row r="295">
@@ -18412,14 +18412,14 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Stanton Sq &amp; Arlington Dr</t>
+          <t>100 East 10th Street</t>
         </is>
       </c>
       <c r="D295" s="2">
-        <v>453.82</v>
+        <v>317.82</v>
       </c>
       <c r="E295" s="2">
-        <v>437.82</v>
+        <v>301.82</v>
       </c>
       <c r="F295" s="2">
         <v>7</v>
@@ -18433,10 +18433,10 @@
         </is>
       </c>
       <c r="I295" s="2">
-        <v>62.5457142857143</v>
+        <v>43.1171428571429</v>
       </c>
       <c r="J295" s="2">
-        <v>69878.9725</v>
+        <v>69742.9725</v>
       </c>
       <c r="K295" s="2">
         <v>0</v>
@@ -18449,14 +18449,14 @@
       </c>
       <c r="O295" t="inlineStr">
         <is>
-          <t>Home to Stanton</t>
+          <t>Stanton to 10th</t>
         </is>
       </c>
       <c r="P295" s="2">
-        <v>7.5</v>
+        <v>2.3</v>
       </c>
       <c r="S295" s="2">
-        <v>67.42428</v>
+        <v>46.48028</v>
       </c>
     </row>
     <row r="296">
@@ -18470,20 +18470,20 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>100 East 10th Street</t>
+          <t>Greenville Blvd &amp; Red Banks Rd</t>
         </is>
       </c>
       <c r="D296" s="2">
-        <v>317.82</v>
+        <v>217.4</v>
       </c>
       <c r="E296" s="2">
-        <v>301.82</v>
+        <v>209.4</v>
       </c>
       <c r="F296" s="2">
         <v>7</v>
       </c>
       <c r="G296" s="2">
-        <v>1191</v>
+        <v>197</v>
       </c>
       <c r="H296" t="inlineStr">
         <is>
@@ -18491,10 +18491,10 @@
         </is>
       </c>
       <c r="I296" s="2">
-        <v>43.1171428571429</v>
+        <v>29.9142857142857</v>
       </c>
       <c r="J296" s="2">
-        <v>70180.7925</v>
+        <v>69952.3725</v>
       </c>
       <c r="K296" s="2">
         <v>0</v>
@@ -18507,14 +18507,14 @@
       </c>
       <c r="O296" t="inlineStr">
         <is>
-          <t>Stanton to 10th</t>
+          <t>10th to Red Banks</t>
         </is>
       </c>
       <c r="P296" s="2">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="S296" s="2">
-        <v>46.48028</v>
+        <v>32.2476</v>
       </c>
     </row>
     <row r="297">
@@ -18528,20 +18528,20 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Greenville Blvd &amp; Red Banks Rd</t>
+          <t>Stanton Sq &amp; Arlington Dr</t>
         </is>
       </c>
       <c r="D297" s="2">
-        <v>217.4</v>
+        <v>453.82</v>
       </c>
       <c r="E297" s="2">
-        <v>209.4</v>
+        <v>437.82</v>
       </c>
       <c r="F297" s="2">
         <v>7</v>
       </c>
       <c r="G297" s="2">
-        <v>1191</v>
+        <v>197</v>
       </c>
       <c r="H297" t="inlineStr">
         <is>
@@ -18549,7 +18549,7 @@
         </is>
       </c>
       <c r="I297" s="2">
-        <v>29.9142857142857</v>
+        <v>62.5457142857143</v>
       </c>
       <c r="J297" s="2">
         <v>70390.1925</v>
@@ -18565,14 +18565,14 @@
       </c>
       <c r="O297" t="inlineStr">
         <is>
-          <t>10th to Red Banks</t>
+          <t>Home to Stanton</t>
         </is>
       </c>
       <c r="P297" s="2">
-        <v>1.9</v>
+        <v>7.5</v>
       </c>
       <c r="S297" s="2">
-        <v>32.2476</v>
+        <v>67.42428</v>
       </c>
     </row>
     <row r="298">
@@ -18599,7 +18599,7 @@
         <v>7</v>
       </c>
       <c r="G298" s="2">
-        <v>1191</v>
+        <v>42</v>
       </c>
       <c r="H298" t="inlineStr">
         <is>
@@ -18631,6 +18631,1650 @@
       </c>
       <c r="S298" s="2">
         <v>31.88724</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="2">
+        <v>32</v>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>100 East 10th Street</t>
+        </is>
+      </c>
+      <c r="D299" s="2">
+        <v>314.06</v>
+      </c>
+      <c r="E299" s="2">
+        <v>298.06</v>
+      </c>
+      <c r="F299" s="2">
+        <v>8</v>
+      </c>
+      <c r="G299" s="2">
+        <v>1199</v>
+      </c>
+      <c r="H299" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I299" s="2">
+        <v>37.2575</v>
+      </c>
+      <c r="J299" s="2">
+        <v>70895.3125</v>
+      </c>
+      <c r="K299" s="2">
+        <v>0</v>
+      </c>
+      <c r="M299" s="2">
+        <v>3.44</v>
+      </c>
+      <c r="N299" s="2">
+        <v>0</v>
+      </c>
+      <c r="O299" t="inlineStr">
+        <is>
+          <t>Stanton to 10th</t>
+        </is>
+      </c>
+      <c r="P299" s="2">
+        <v>2.3</v>
+      </c>
+      <c r="S299" s="2">
+        <v>45.90124</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="2">
+        <v>32</v>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>Greenville Blvd &amp; Red Banks Rd</t>
+        </is>
+      </c>
+      <c r="D300" s="2">
+        <v>273.1</v>
+      </c>
+      <c r="E300" s="2">
+        <v>265.1</v>
+      </c>
+      <c r="F300" s="2">
+        <v>8</v>
+      </c>
+      <c r="G300" s="2">
+        <v>205</v>
+      </c>
+      <c r="H300" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I300" s="2">
+        <v>33.1375</v>
+      </c>
+      <c r="J300" s="2">
+        <v>71160.4125</v>
+      </c>
+      <c r="K300" s="2">
+        <v>0</v>
+      </c>
+      <c r="M300" s="2">
+        <v>0</v>
+      </c>
+      <c r="N300" s="2">
+        <v>0</v>
+      </c>
+      <c r="O300" t="inlineStr">
+        <is>
+          <t>10th to Red Banks</t>
+        </is>
+      </c>
+      <c r="P300" s="2">
+        <v>1.9</v>
+      </c>
+      <c r="S300" s="2">
+        <v>40.8254</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="2">
+        <v>32</v>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>Stanton Sq &amp; Arlington Dr</t>
+        </is>
+      </c>
+      <c r="D301" s="2">
+        <v>493.76</v>
+      </c>
+      <c r="E301" s="2">
+        <v>469.76</v>
+      </c>
+      <c r="F301" s="2">
+        <v>8</v>
+      </c>
+      <c r="G301" s="2">
+        <v>205</v>
+      </c>
+      <c r="H301" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I301" s="2">
+        <v>58.72</v>
+      </c>
+      <c r="J301" s="2">
+        <v>71630.1725</v>
+      </c>
+      <c r="K301" s="2">
+        <v>0</v>
+      </c>
+      <c r="M301" s="2">
+        <v>0</v>
+      </c>
+      <c r="N301" s="2">
+        <v>0</v>
+      </c>
+      <c r="O301" t="inlineStr">
+        <is>
+          <t>Home to Stanton</t>
+        </is>
+      </c>
+      <c r="P301" s="2">
+        <v>7.5</v>
+      </c>
+      <c r="S301" s="2">
+        <v>72.34304</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="2">
+        <v>32</v>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>Winterville</t>
+        </is>
+      </c>
+      <c r="D302" s="2">
+        <v>231.06</v>
+      </c>
+      <c r="E302" s="2">
+        <v>215.06</v>
+      </c>
+      <c r="F302" s="2">
+        <v>8</v>
+      </c>
+      <c r="G302" s="2">
+        <v>50</v>
+      </c>
+      <c r="H302" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I302" s="2">
+        <v>26.8825</v>
+      </c>
+      <c r="J302" s="2">
+        <v>71845.2325</v>
+      </c>
+      <c r="K302" s="2">
+        <v>0</v>
+      </c>
+      <c r="M302" s="2">
+        <v>0</v>
+      </c>
+      <c r="N302" s="2">
+        <v>0</v>
+      </c>
+      <c r="O302" t="inlineStr">
+        <is>
+          <t>Red Banks to Winterville to Home</t>
+        </is>
+      </c>
+      <c r="P302" s="2">
+        <v>14.2</v>
+      </c>
+      <c r="S302" s="2">
+        <v>33.11924</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="2">
+        <v>33</v>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>100 East 10th Street</t>
+        </is>
+      </c>
+      <c r="D303" s="2">
+        <v>394.32</v>
+      </c>
+      <c r="E303" s="2">
+        <v>378.32</v>
+      </c>
+      <c r="F303" s="2">
+        <v>8</v>
+      </c>
+      <c r="G303" s="2">
+        <v>1207</v>
+      </c>
+      <c r="H303" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I303" s="2">
+        <v>47.29</v>
+      </c>
+      <c r="J303" s="2">
+        <v>72223.5525</v>
+      </c>
+      <c r="K303" s="2">
+        <v>0</v>
+      </c>
+      <c r="M303" s="2">
+        <v>12</v>
+      </c>
+      <c r="N303" s="2">
+        <v>0</v>
+      </c>
+      <c r="O303" t="inlineStr">
+        <is>
+          <t>Stanton to 10th</t>
+        </is>
+      </c>
+      <c r="P303" s="2">
+        <v>2.3</v>
+      </c>
+      <c r="S303" s="2">
+        <v>58.26128</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="2">
+        <v>33</v>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>Greenville Blvd &amp; Red Banks Rd</t>
+        </is>
+      </c>
+      <c r="D304" s="2">
+        <v>291.62</v>
+      </c>
+      <c r="E304" s="2">
+        <v>275.62</v>
+      </c>
+      <c r="F304" s="2">
+        <v>8</v>
+      </c>
+      <c r="G304" s="2">
+        <v>213</v>
+      </c>
+      <c r="H304" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I304" s="2">
+        <v>34.4525</v>
+      </c>
+      <c r="J304" s="2">
+        <v>72499.1725</v>
+      </c>
+      <c r="K304" s="2">
+        <v>0</v>
+      </c>
+      <c r="M304" s="2">
+        <v>0</v>
+      </c>
+      <c r="N304" s="2">
+        <v>0</v>
+      </c>
+      <c r="O304" t="inlineStr">
+        <is>
+          <t>10th to Red Banks</t>
+        </is>
+      </c>
+      <c r="P304" s="2">
+        <v>1.9</v>
+      </c>
+      <c r="S304" s="2">
+        <v>42.44548</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="2">
+        <v>33</v>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>Stanton Sq &amp; Arlington Dr</t>
+        </is>
+      </c>
+      <c r="D305" s="2">
+        <v>442.96</v>
+      </c>
+      <c r="E305" s="2">
+        <v>426.96</v>
+      </c>
+      <c r="F305" s="2">
+        <v>8</v>
+      </c>
+      <c r="G305" s="2">
+        <v>213</v>
+      </c>
+      <c r="H305" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I305" s="2">
+        <v>53.37</v>
+      </c>
+      <c r="J305" s="2">
+        <v>72926.1325</v>
+      </c>
+      <c r="K305" s="2">
+        <v>0</v>
+      </c>
+      <c r="M305" s="2">
+        <v>0</v>
+      </c>
+      <c r="N305" s="2">
+        <v>0</v>
+      </c>
+      <c r="O305" t="inlineStr">
+        <is>
+          <t>Home to Stanton</t>
+        </is>
+      </c>
+      <c r="P305" s="2">
+        <v>7.5</v>
+      </c>
+      <c r="S305" s="2">
+        <v>65.75184</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="2">
+        <v>33</v>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>Winterville</t>
+        </is>
+      </c>
+      <c r="D306" s="2">
+        <v>267.96</v>
+      </c>
+      <c r="E306" s="2">
+        <v>251.96</v>
+      </c>
+      <c r="F306" s="2">
+        <v>8</v>
+      </c>
+      <c r="G306" s="2">
+        <v>58</v>
+      </c>
+      <c r="H306" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I306" s="2">
+        <v>31.495</v>
+      </c>
+      <c r="J306" s="2">
+        <v>73178.0925</v>
+      </c>
+      <c r="K306" s="2">
+        <v>0</v>
+      </c>
+      <c r="M306" s="2">
+        <v>2.56</v>
+      </c>
+      <c r="N306" s="2">
+        <v>0</v>
+      </c>
+      <c r="O306" t="inlineStr">
+        <is>
+          <t>Red Banks to Winterville to Home</t>
+        </is>
+      </c>
+      <c r="P306" s="2">
+        <v>14.2</v>
+      </c>
+      <c r="S306" s="2">
+        <v>38.80184</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="2">
+        <v>34</v>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>Greenville Blvd &amp; Red Banks Rd</t>
+        </is>
+      </c>
+      <c r="D307" s="2">
+        <v>128.48</v>
+      </c>
+      <c r="E307" s="2">
+        <v>120.48</v>
+      </c>
+      <c r="F307" s="2">
+        <v>4</v>
+      </c>
+      <c r="G307" s="2">
+        <v>217</v>
+      </c>
+      <c r="H307" t="inlineStr">
+        <is>
+          <t>Me</t>
+        </is>
+      </c>
+      <c r="I307" s="2">
+        <v>30.12</v>
+      </c>
+      <c r="J307" s="2">
+        <v>73298.5725</v>
+      </c>
+      <c r="K307" s="2">
+        <v>0</v>
+      </c>
+      <c r="M307" s="2">
+        <v>0</v>
+      </c>
+      <c r="N307" s="2">
+        <v>0</v>
+      </c>
+      <c r="O307" t="inlineStr">
+        <is>
+          <t>Home to Trinity to Red Banks</t>
+        </is>
+      </c>
+      <c r="P307" s="2">
+        <v>7.6</v>
+      </c>
+      <c r="S307" s="2">
+        <v>18.55392</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="2">
+        <v>34</v>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>Winterville</t>
+        </is>
+      </c>
+      <c r="D308" s="2">
+        <v>105.2</v>
+      </c>
+      <c r="E308" s="2">
+        <v>97.2</v>
+      </c>
+      <c r="F308" s="2">
+        <v>4</v>
+      </c>
+      <c r="G308" s="2">
+        <v>62</v>
+      </c>
+      <c r="H308" t="inlineStr">
+        <is>
+          <t>Me</t>
+        </is>
+      </c>
+      <c r="I308" s="2">
+        <v>24.3</v>
+      </c>
+      <c r="J308" s="2">
+        <v>73395.7725</v>
+      </c>
+      <c r="K308" s="2">
+        <v>0</v>
+      </c>
+      <c r="M308" s="2">
+        <v>0</v>
+      </c>
+      <c r="N308" s="2">
+        <v>0</v>
+      </c>
+      <c r="O308" t="inlineStr">
+        <is>
+          <t>Red Banks to Winterville</t>
+        </is>
+      </c>
+      <c r="P308" s="2">
+        <v>3.8</v>
+      </c>
+      <c r="S308" s="2">
+        <v>14.9688</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="2">
+        <v>34</v>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>Stanton Sq &amp; Arlington Dr</t>
+        </is>
+      </c>
+      <c r="D309" s="2">
+        <v>188.1</v>
+      </c>
+      <c r="E309" s="2">
+        <v>180.1</v>
+      </c>
+      <c r="F309" s="2">
+        <v>4</v>
+      </c>
+      <c r="G309" s="2">
+        <v>217</v>
+      </c>
+      <c r="H309" t="inlineStr">
+        <is>
+          <t>Me</t>
+        </is>
+      </c>
+      <c r="I309" s="2">
+        <v>45.025</v>
+      </c>
+      <c r="J309" s="2">
+        <v>73575.8725</v>
+      </c>
+      <c r="K309" s="2">
+        <v>0</v>
+      </c>
+      <c r="M309" s="2">
+        <v>0</v>
+      </c>
+      <c r="N309" s="2">
+        <v>0</v>
+      </c>
+      <c r="O309" t="inlineStr">
+        <is>
+          <t>Winterville to Stanton</t>
+        </is>
+      </c>
+      <c r="P309" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="S309" s="2">
+        <v>27.7354</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="2">
+        <v>34</v>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>100 East 10th Street</t>
+        </is>
+      </c>
+      <c r="D310" s="2">
+        <v>262.12</v>
+      </c>
+      <c r="E310" s="2">
+        <v>246.12</v>
+      </c>
+      <c r="F310" s="2">
+        <v>4</v>
+      </c>
+      <c r="G310" s="2">
+        <v>1211</v>
+      </c>
+      <c r="H310" t="inlineStr">
+        <is>
+          <t>Me</t>
+        </is>
+      </c>
+      <c r="I310" s="2">
+        <v>61.53</v>
+      </c>
+      <c r="J310" s="2">
+        <v>73821.9925</v>
+      </c>
+      <c r="K310" s="2">
+        <v>0</v>
+      </c>
+      <c r="M310" s="2">
+        <v>0</v>
+      </c>
+      <c r="N310" s="2">
+        <v>0</v>
+      </c>
+      <c r="O310" t="inlineStr">
+        <is>
+          <t>Stanton to 10th to Home</t>
+        </is>
+      </c>
+      <c r="P310" s="2">
+        <v>7.9</v>
+      </c>
+      <c r="S310" s="2">
+        <v>37.90248</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="2">
+        <v>35</v>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>Greenville Blvd &amp; Red Banks Rd</t>
+        </is>
+      </c>
+      <c r="D311" s="2">
+        <v>196.56</v>
+      </c>
+      <c r="E311" s="2">
+        <v>188.56</v>
+      </c>
+      <c r="F311" s="2">
+        <v>7</v>
+      </c>
+      <c r="G311" s="2">
+        <v>224</v>
+      </c>
+      <c r="H311" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I311" s="2">
+        <v>26.9371428571429</v>
+      </c>
+      <c r="J311" s="2">
+        <v>74010.5525</v>
+      </c>
+      <c r="K311" s="2">
+        <v>0</v>
+      </c>
+      <c r="M311" s="2">
+        <v>0</v>
+      </c>
+      <c r="N311" s="2">
+        <v>0</v>
+      </c>
+      <c r="O311" t="inlineStr">
+        <is>
+          <t>Home to Trinity to Red Banks</t>
+        </is>
+      </c>
+      <c r="P311" s="2">
+        <v>7.6</v>
+      </c>
+      <c r="S311" s="2">
+        <v>29.03824</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="2">
+        <v>35</v>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>Winterville</t>
+        </is>
+      </c>
+      <c r="D312" s="2">
+        <v>150.6</v>
+      </c>
+      <c r="E312" s="2">
+        <v>142.6</v>
+      </c>
+      <c r="F312" s="2">
+        <v>7</v>
+      </c>
+      <c r="G312" s="2">
+        <v>69</v>
+      </c>
+      <c r="H312" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I312" s="2">
+        <v>20.3714285714286</v>
+      </c>
+      <c r="J312" s="2">
+        <v>74153.1525</v>
+      </c>
+      <c r="K312" s="2">
+        <v>0</v>
+      </c>
+      <c r="M312" s="2">
+        <v>0</v>
+      </c>
+      <c r="N312" s="2">
+        <v>0</v>
+      </c>
+      <c r="O312" t="inlineStr">
+        <is>
+          <t>Red Banks to Winterville</t>
+        </is>
+      </c>
+      <c r="P312" s="2">
+        <v>3.8</v>
+      </c>
+      <c r="S312" s="2">
+        <v>21.9604</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="2">
+        <v>35</v>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>Stanton Sq &amp; Arlington Dr</t>
+        </is>
+      </c>
+      <c r="D313" s="2">
+        <v>314.52</v>
+      </c>
+      <c r="E313" s="2">
+        <v>298.52</v>
+      </c>
+      <c r="F313" s="2">
+        <v>7</v>
+      </c>
+      <c r="G313" s="2">
+        <v>224</v>
+      </c>
+      <c r="H313" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I313" s="2">
+        <v>42.6457142857143</v>
+      </c>
+      <c r="J313" s="2">
+        <v>74451.6725</v>
+      </c>
+      <c r="K313" s="2">
+        <v>0</v>
+      </c>
+      <c r="M313" s="2">
+        <v>0</v>
+      </c>
+      <c r="N313" s="2">
+        <v>0</v>
+      </c>
+      <c r="O313" t="inlineStr">
+        <is>
+          <t>Winterville to Stanton</t>
+        </is>
+      </c>
+      <c r="P313" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="S313" s="2">
+        <v>45.97208</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="2">
+        <v>35</v>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>100 East 10th Street</t>
+        </is>
+      </c>
+      <c r="D314" s="2">
+        <v>321.42</v>
+      </c>
+      <c r="E314" s="2">
+        <v>305.42</v>
+      </c>
+      <c r="F314" s="2">
+        <v>7</v>
+      </c>
+      <c r="G314" s="2">
+        <v>1218</v>
+      </c>
+      <c r="H314" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I314" s="2">
+        <v>43.6314285714286</v>
+      </c>
+      <c r="J314" s="2">
+        <v>74757.0925</v>
+      </c>
+      <c r="K314" s="2">
+        <v>0</v>
+      </c>
+      <c r="M314" s="2">
+        <v>30.94</v>
+      </c>
+      <c r="N314" s="2">
+        <v>0</v>
+      </c>
+      <c r="O314" t="inlineStr">
+        <is>
+          <t>Stanton to 10th to Home</t>
+        </is>
+      </c>
+      <c r="P314" s="2">
+        <v>7.9</v>
+      </c>
+      <c r="S314" s="2">
+        <v>47.03468</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="2">
+        <v>36</v>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>100 East 10th Street</t>
+        </is>
+      </c>
+      <c r="D315" s="2">
+        <v>364.93</v>
+      </c>
+      <c r="E315" s="2">
+        <v>340.93</v>
+      </c>
+      <c r="F315" s="2">
+        <v>7</v>
+      </c>
+      <c r="G315" s="2">
+        <v>1225</v>
+      </c>
+      <c r="H315" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I315" s="2">
+        <v>48.7042857142857</v>
+      </c>
+      <c r="J315" s="2">
+        <v>75098.0225</v>
+      </c>
+      <c r="K315" s="2">
+        <v>0</v>
+      </c>
+      <c r="M315" s="2">
+        <v>0</v>
+      </c>
+      <c r="N315" s="2">
+        <v>0</v>
+      </c>
+      <c r="O315" t="inlineStr">
+        <is>
+          <t>Trinity to 100 East 10th Street</t>
+        </is>
+      </c>
+      <c r="P315" s="2">
+        <v>13.5</v>
+      </c>
+      <c r="S315" s="2">
+        <v>52.50322</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="2">
+        <v>36</v>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>Greenville Blvd &amp; Red Banks Rd</t>
+        </is>
+      </c>
+      <c r="D316" s="2">
+        <v>241.1</v>
+      </c>
+      <c r="E316" s="2">
+        <v>225.1</v>
+      </c>
+      <c r="F316" s="2">
+        <v>7</v>
+      </c>
+      <c r="G316" s="2">
+        <v>231</v>
+      </c>
+      <c r="H316" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I316" s="2">
+        <v>32.1571428571429</v>
+      </c>
+      <c r="J316" s="2">
+        <v>75323.1225</v>
+      </c>
+      <c r="K316" s="2">
+        <v>0</v>
+      </c>
+      <c r="M316" s="2">
+        <v>0</v>
+      </c>
+      <c r="N316" s="2">
+        <v>0</v>
+      </c>
+      <c r="O316" t="inlineStr">
+        <is>
+          <t>10th to Red Banks</t>
+        </is>
+      </c>
+      <c r="P316" s="2">
+        <v>1.9</v>
+      </c>
+      <c r="S316" s="2">
+        <v>34.6654</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="2">
+        <v>36</v>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>Winterville</t>
+        </is>
+      </c>
+      <c r="D317" s="2">
+        <v>199.84</v>
+      </c>
+      <c r="E317" s="2">
+        <v>191.84</v>
+      </c>
+      <c r="F317" s="2">
+        <v>7</v>
+      </c>
+      <c r="G317" s="2">
+        <v>76</v>
+      </c>
+      <c r="H317" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I317" s="2">
+        <v>27.4057142857143</v>
+      </c>
+      <c r="J317" s="2">
+        <v>75514.9625</v>
+      </c>
+      <c r="K317" s="2">
+        <v>0</v>
+      </c>
+      <c r="M317" s="2">
+        <v>0</v>
+      </c>
+      <c r="N317" s="2">
+        <v>0</v>
+      </c>
+      <c r="O317" t="inlineStr">
+        <is>
+          <t>Red Banks to Winterville</t>
+        </is>
+      </c>
+      <c r="P317" s="2">
+        <v>3.8</v>
+      </c>
+      <c r="S317" s="2">
+        <v>29.54336</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="2">
+        <v>36</v>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>Stanton Sq &amp; Arlington Dr</t>
+        </is>
+      </c>
+      <c r="D318" s="2">
+        <v>361.5</v>
+      </c>
+      <c r="E318" s="2">
+        <v>345.5</v>
+      </c>
+      <c r="F318" s="2">
+        <v>7</v>
+      </c>
+      <c r="G318" s="2">
+        <v>231</v>
+      </c>
+      <c r="H318" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I318" s="2">
+        <v>49.3571428571429</v>
+      </c>
+      <c r="J318" s="2">
+        <v>75860.4625</v>
+      </c>
+      <c r="K318" s="2">
+        <v>0</v>
+      </c>
+      <c r="M318" s="2">
+        <v>0</v>
+      </c>
+      <c r="N318" s="2">
+        <v>0</v>
+      </c>
+      <c r="O318" t="inlineStr">
+        <is>
+          <t>Winterville to Stanton to Home</t>
+        </is>
+      </c>
+      <c r="P318" s="2">
+        <v>12.2</v>
+      </c>
+      <c r="S318" s="2">
+        <v>53.207</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="2">
+        <v>37</v>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>100 East 10th Street</t>
+        </is>
+      </c>
+      <c r="D319" s="2">
+        <v>381.9</v>
+      </c>
+      <c r="E319" s="2">
+        <v>365.9</v>
+      </c>
+      <c r="F319" s="2">
+        <v>7</v>
+      </c>
+      <c r="G319" s="2">
+        <v>1232</v>
+      </c>
+      <c r="H319" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I319" s="2">
+        <v>52.2714285714286</v>
+      </c>
+      <c r="J319" s="2">
+        <v>76226.3625</v>
+      </c>
+      <c r="K319" s="2">
+        <v>0</v>
+      </c>
+      <c r="M319" s="2">
+        <v>0</v>
+      </c>
+      <c r="N319" s="2">
+        <v>0</v>
+      </c>
+      <c r="O319" t="inlineStr">
+        <is>
+          <t>Home to 10th</t>
+        </is>
+      </c>
+      <c r="P319" s="2">
+        <v>6.9</v>
+      </c>
+      <c r="S319" s="2">
+        <v>56.3486</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="2">
+        <v>37</v>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>Greenville Blvd &amp; Red Banks Rd</t>
+        </is>
+      </c>
+      <c r="D320" s="2">
+        <v>240.5</v>
+      </c>
+      <c r="E320" s="2">
+        <v>224.5</v>
+      </c>
+      <c r="F320" s="2">
+        <v>7</v>
+      </c>
+      <c r="G320" s="2">
+        <v>238</v>
+      </c>
+      <c r="H320" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I320" s="2">
+        <v>32.0714285714286</v>
+      </c>
+      <c r="J320" s="2">
+        <v>76450.8625</v>
+      </c>
+      <c r="K320" s="2">
+        <v>0</v>
+      </c>
+      <c r="M320" s="2">
+        <v>0</v>
+      </c>
+      <c r="N320" s="2">
+        <v>0</v>
+      </c>
+      <c r="O320" t="inlineStr">
+        <is>
+          <t>10th to Red Banks</t>
+        </is>
+      </c>
+      <c r="P320" s="2">
+        <v>1.9</v>
+      </c>
+      <c r="S320" s="2">
+        <v>34.573</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="2">
+        <v>37</v>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>Winterville</t>
+        </is>
+      </c>
+      <c r="D321" s="2">
+        <v>244</v>
+      </c>
+      <c r="E321" s="2">
+        <v>215</v>
+      </c>
+      <c r="F321" s="2">
+        <v>7</v>
+      </c>
+      <c r="G321" s="2">
+        <v>83</v>
+      </c>
+      <c r="H321" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I321" s="2">
+        <v>30.7142857142857</v>
+      </c>
+      <c r="J321" s="2">
+        <v>76665.8625</v>
+      </c>
+      <c r="K321" s="2">
+        <v>0</v>
+      </c>
+      <c r="M321" s="2">
+        <v>0</v>
+      </c>
+      <c r="N321" s="2">
+        <v>0</v>
+      </c>
+      <c r="O321" t="inlineStr">
+        <is>
+          <t>Red Banks to Winterville</t>
+        </is>
+      </c>
+      <c r="P321" s="2">
+        <v>3.8</v>
+      </c>
+      <c r="R321" t="inlineStr">
+        <is>
+          <t>This is the 1st pickup using 65gal cart. Everything went well. We will transition to these carts for all stores. </t>
+        </is>
+      </c>
+      <c r="S321" s="2">
+        <v>33.11</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="2">
+        <v>37</v>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>Stanton Sq &amp; Arlington Dr</t>
+        </is>
+      </c>
+      <c r="D322" s="2">
+        <v>475.374</v>
+      </c>
+      <c r="E322" s="2">
+        <v>459.374</v>
+      </c>
+      <c r="F322" s="2">
+        <v>7</v>
+      </c>
+      <c r="G322" s="2">
+        <v>238</v>
+      </c>
+      <c r="H322" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I322" s="2">
+        <v>65.6248571428572</v>
+      </c>
+      <c r="J322" s="2">
+        <v>77125.2365</v>
+      </c>
+      <c r="K322" s="2">
+        <v>0</v>
+      </c>
+      <c r="M322" s="2">
+        <v>0</v>
+      </c>
+      <c r="N322" s="2">
+        <v>0</v>
+      </c>
+      <c r="O322" t="inlineStr">
+        <is>
+          <t>Winterville to Stanton to Home</t>
+        </is>
+      </c>
+      <c r="P322" s="2">
+        <v>12.2</v>
+      </c>
+      <c r="S322" s="2">
+        <v>70.743596</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="2">
+        <v>38</v>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>Greenville Blvd &amp; Red Banks Rd</t>
+        </is>
+      </c>
+      <c r="D323" s="2">
+        <v>228.58</v>
+      </c>
+      <c r="E323" s="2">
+        <v>212.58</v>
+      </c>
+      <c r="F323" s="2">
+        <v>7</v>
+      </c>
+      <c r="G323" s="2">
+        <v>245</v>
+      </c>
+      <c r="H323" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I323" s="2">
+        <v>30.3685714285714</v>
+      </c>
+      <c r="J323" s="2">
+        <v>77337.8165</v>
+      </c>
+      <c r="K323" s="2">
+        <v>0</v>
+      </c>
+      <c r="M323" s="2">
+        <v>0</v>
+      </c>
+      <c r="N323" s="2">
+        <v>0</v>
+      </c>
+      <c r="O323" t="inlineStr">
+        <is>
+          <t>Home to Trinity to Red Banks</t>
+        </is>
+      </c>
+      <c r="P323" s="2">
+        <v>7.6</v>
+      </c>
+      <c r="R323" t="inlineStr">
+        <is>
+          <t>Dropped off 1x65 gallon carts, replacing 32 gallon bins</t>
+        </is>
+      </c>
+      <c r="S323" s="2">
+        <v>32.73732</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="2">
+        <v>38</v>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>Winterville</t>
+        </is>
+      </c>
+      <c r="D324" s="2">
+        <v>134.52</v>
+      </c>
+      <c r="E324" s="2">
+        <v>105.52</v>
+      </c>
+      <c r="F324" s="2">
+        <v>7</v>
+      </c>
+      <c r="G324" s="2">
+        <v>90</v>
+      </c>
+      <c r="H324" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I324" s="2">
+        <v>15.0742857142857</v>
+      </c>
+      <c r="J324" s="2">
+        <v>77443.3365</v>
+      </c>
+      <c r="K324" s="2">
+        <v>0</v>
+      </c>
+      <c r="M324" s="2">
+        <v>0</v>
+      </c>
+      <c r="N324" s="2">
+        <v>0</v>
+      </c>
+      <c r="O324" t="inlineStr">
+        <is>
+          <t>Red Banks to Winterville</t>
+        </is>
+      </c>
+      <c r="P324" s="2">
+        <v>3.8</v>
+      </c>
+      <c r="S324" s="2">
+        <v>16.25008</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="2">
+        <v>38</v>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>Stanton Sq &amp; Arlington Dr</t>
+        </is>
+      </c>
+      <c r="D325" s="2">
+        <v>387.6</v>
+      </c>
+      <c r="E325" s="2">
+        <v>371.6</v>
+      </c>
+      <c r="F325" s="2">
+        <v>7</v>
+      </c>
+      <c r="G325" s="2">
+        <v>245</v>
+      </c>
+      <c r="H325" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I325" s="2">
+        <v>53.0857142857143</v>
+      </c>
+      <c r="J325" s="2">
+        <v>77814.9365</v>
+      </c>
+      <c r="K325" s="2">
+        <v>0</v>
+      </c>
+      <c r="M325" s="2">
+        <v>0</v>
+      </c>
+      <c r="N325" s="2">
+        <v>0</v>
+      </c>
+      <c r="O325" t="inlineStr">
+        <is>
+          <t>Winterville to Stanton</t>
+        </is>
+      </c>
+      <c r="P325" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="R325" t="inlineStr">
+        <is>
+          <t>Dropped off 2x65 gallon carts, replacing 32 gallon bins</t>
+        </is>
+      </c>
+      <c r="S325" s="2">
+        <v>57.2264</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="2">
+        <v>38</v>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>100 East 10th Street</t>
+        </is>
+      </c>
+      <c r="D326" s="2">
+        <v>386.02</v>
+      </c>
+      <c r="E326" s="2">
+        <v>370.02</v>
+      </c>
+      <c r="F326" s="2">
+        <v>7</v>
+      </c>
+      <c r="G326" s="2">
+        <v>1239</v>
+      </c>
+      <c r="H326" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I326" s="2">
+        <v>52.86</v>
+      </c>
+      <c r="J326" s="2">
+        <v>78184.9565</v>
+      </c>
+      <c r="K326" s="2">
+        <v>0</v>
+      </c>
+      <c r="M326" s="2">
+        <v>0</v>
+      </c>
+      <c r="N326" s="2">
+        <v>0</v>
+      </c>
+      <c r="O326" t="inlineStr">
+        <is>
+          <t>Stanton to 10th to Home</t>
+        </is>
+      </c>
+      <c r="P326" s="2">
+        <v>7.9</v>
+      </c>
+      <c r="R326" t="inlineStr">
+        <is>
+          <t>Dropped off 2x65 gallon carts, replacing 32 gallon bins</t>
+        </is>
+      </c>
+      <c r="S326" s="2">
+        <v>56.98308</v>
       </c>
     </row>
   </sheetData>
